--- a/research/traditional_assets/database/data/austria/austria_oilfield_svcs_equip.xlsx
+++ b/research/traditional_assets/database/data/austria/austria_oilfield_svcs_equip.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08467486899156748</v>
+        <v>0.08450584930598772</v>
       </c>
       <c r="C2">
-        <v>840.081058236009</v>
+        <v>832.842033922926</v>
       </c>
       <c r="D2">
-        <v>546.4810582360089</v>
+        <v>548.125033922926</v>
       </c>
       <c r="E2">
-        <v>-402.1</v>
+        <v>-393.217</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>8.882999999999999</v>
       </c>
       <c r="G2">
         <v>293.6</v>
@@ -1451,28 +1451,28 @@
         <v>88.7</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.4468149</v>
       </c>
       <c r="N2">
-        <v>88.7</v>
+        <v>88.2531851</v>
       </c>
       <c r="O2">
-        <v>21.288</v>
+        <v>21.180764424</v>
       </c>
       <c r="P2">
-        <v>67.41200000000001</v>
+        <v>67.07242067599999</v>
       </c>
       <c r="Q2">
-        <v>99.812</v>
+        <v>99.47242067599998</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08467486899156748</v>
+        <v>0.08497330232928052</v>
       </c>
       <c r="T2">
-        <v>0.7993082229751833</v>
+        <v>0.8054443265050939</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>198.5162088372612</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08450584930598772</v>
+        <v>0.08433682962040795</v>
       </c>
       <c r="C3">
-        <v>832.842033922926</v>
+        <v>825.6129305794165</v>
       </c>
       <c r="D3">
-        <v>548.125033922926</v>
+        <v>549.7789305794164</v>
       </c>
       <c r="E3">
-        <v>-393.217</v>
+        <v>-384.334</v>
       </c>
       <c r="F3">
-        <v>8.882999999999999</v>
+        <v>17.766</v>
       </c>
       <c r="G3">
         <v>293.6</v>
@@ -1533,28 +1533,28 @@
         <v>88.7</v>
       </c>
       <c r="M3">
-        <v>0.4468149</v>
+        <v>0.8936297999999999</v>
       </c>
       <c r="N3">
-        <v>88.2531851</v>
+        <v>87.8063702</v>
       </c>
       <c r="O3">
-        <v>21.180764424</v>
+        <v>21.073528848</v>
       </c>
       <c r="P3">
-        <v>67.07242067599999</v>
+        <v>66.73284135200001</v>
       </c>
       <c r="Q3">
-        <v>99.47242067599998</v>
+        <v>99.132841352</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08497330232928052</v>
+        <v>0.08527782614327342</v>
       </c>
       <c r="T3">
-        <v>0.8054443265050939</v>
+        <v>0.8117056566376556</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>198.5162088372612</v>
+        <v>99.25810441863064</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08433682962040795</v>
+        <v>0.08416780993482818</v>
       </c>
       <c r="C4">
-        <v>825.6129305794165</v>
+        <v>818.3938382830191</v>
       </c>
       <c r="D4">
-        <v>549.7789305794164</v>
+        <v>551.4428382830191</v>
       </c>
       <c r="E4">
-        <v>-384.334</v>
+        <v>-375.451</v>
       </c>
       <c r="F4">
-        <v>17.766</v>
+        <v>26.649</v>
       </c>
       <c r="G4">
         <v>293.6</v>
@@ -1615,28 +1615,28 @@
         <v>88.7</v>
       </c>
       <c r="M4">
-        <v>0.8936297999999999</v>
+        <v>1.3404447</v>
       </c>
       <c r="N4">
-        <v>87.8063702</v>
+        <v>87.3595553</v>
       </c>
       <c r="O4">
-        <v>21.073528848</v>
+        <v>20.966293272</v>
       </c>
       <c r="P4">
-        <v>66.73284135200001</v>
+        <v>66.393262028</v>
       </c>
       <c r="Q4">
-        <v>99.132841352</v>
+        <v>98.79326202799999</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08527782614327342</v>
+        <v>0.08558862879879195</v>
       </c>
       <c r="T4">
-        <v>0.8117056566376556</v>
+        <v>0.8180960863605795</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>99.25810441863064</v>
+        <v>66.17206961242043</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08416780993482818</v>
+        <v>0.08399879024924843</v>
       </c>
       <c r="C5">
-        <v>818.3938382830191</v>
+        <v>811.1848482050632</v>
       </c>
       <c r="D5">
-        <v>551.4428382830191</v>
+        <v>553.1168482050632</v>
       </c>
       <c r="E5">
-        <v>-375.451</v>
+        <v>-366.568</v>
       </c>
       <c r="F5">
-        <v>26.649</v>
+        <v>35.532</v>
       </c>
       <c r="G5">
         <v>293.6</v>
@@ -1697,28 +1697,28 @@
         <v>88.7</v>
       </c>
       <c r="M5">
-        <v>1.3404447</v>
+        <v>1.7872596</v>
       </c>
       <c r="N5">
-        <v>87.3595553</v>
+        <v>86.9127404</v>
       </c>
       <c r="O5">
-        <v>20.966293272</v>
+        <v>20.859057696</v>
       </c>
       <c r="P5">
-        <v>66.393262028</v>
+        <v>66.05368270400001</v>
       </c>
       <c r="Q5">
-        <v>98.79326202799999</v>
+        <v>98.453682704</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08558862879879195</v>
+        <v>0.08590590650963378</v>
       </c>
       <c r="T5">
-        <v>0.8180960863605795</v>
+        <v>0.8246196500360642</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>66.17206961242043</v>
+        <v>49.62905220931532</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08399879024924843</v>
+        <v>0.08382977056366867</v>
       </c>
       <c r="C6">
-        <v>811.1848482050632</v>
+        <v>803.9860526273212</v>
       </c>
       <c r="D6">
-        <v>553.1168482050632</v>
+        <v>554.8010526273212</v>
       </c>
       <c r="E6">
-        <v>-366.568</v>
+        <v>-357.685</v>
       </c>
       <c r="F6">
-        <v>35.532</v>
+        <v>44.415</v>
       </c>
       <c r="G6">
         <v>293.6</v>
@@ -1779,28 +1779,28 @@
         <v>88.7</v>
       </c>
       <c r="M6">
-        <v>1.7872596</v>
+        <v>2.2340745</v>
       </c>
       <c r="N6">
-        <v>86.9127404</v>
+        <v>86.4659255</v>
       </c>
       <c r="O6">
-        <v>20.859057696</v>
+        <v>20.75182212</v>
       </c>
       <c r="P6">
-        <v>66.05368270400001</v>
+        <v>65.71410338</v>
       </c>
       <c r="Q6">
-        <v>98.453682704</v>
+        <v>98.11410337999999</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08590590650963378</v>
+        <v>0.08622986375123018</v>
       </c>
       <c r="T6">
-        <v>0.8246196500360642</v>
+        <v>0.8312805518941907</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>49.62905220931532</v>
+        <v>39.70324176745225</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08382977056366867</v>
+        <v>0.0836607508780889</v>
       </c>
       <c r="C7">
-        <v>803.9860526273212</v>
+        <v>796.7975449589655</v>
       </c>
       <c r="D7">
-        <v>554.8010526273212</v>
+        <v>556.4955449589655</v>
       </c>
       <c r="E7">
-        <v>-357.685</v>
+        <v>-348.802</v>
       </c>
       <c r="F7">
-        <v>44.415</v>
+        <v>53.298</v>
       </c>
       <c r="G7">
         <v>293.6</v>
@@ -1861,28 +1861,28 @@
         <v>88.7</v>
       </c>
       <c r="M7">
-        <v>2.2340745</v>
+        <v>2.6808894</v>
       </c>
       <c r="N7">
-        <v>86.4659255</v>
+        <v>86.0191106</v>
       </c>
       <c r="O7">
-        <v>20.75182212</v>
+        <v>20.644586544</v>
       </c>
       <c r="P7">
-        <v>65.71410338</v>
+        <v>65.37452405600001</v>
       </c>
       <c r="Q7">
-        <v>98.11410337999999</v>
+        <v>97.774524056</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.08622986375123018</v>
+        <v>0.08656071370009458</v>
       </c>
       <c r="T7">
-        <v>0.8312805518941907</v>
+        <v>0.8380831750684475</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>39.70324176745225</v>
+        <v>33.08603480621021</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.0836607508780889</v>
+        <v>0.08349173119250916</v>
       </c>
       <c r="C8">
-        <v>796.7975449589655</v>
+        <v>789.6194197538385</v>
       </c>
       <c r="D8">
-        <v>556.4955449589655</v>
+        <v>558.2004197538386</v>
       </c>
       <c r="E8">
-        <v>-348.802</v>
+        <v>-339.919</v>
       </c>
       <c r="F8">
-        <v>53.29799999999999</v>
+        <v>62.18099999999999</v>
       </c>
       <c r="G8">
         <v>293.6</v>
@@ -1943,28 +1943,28 @@
         <v>88.7</v>
       </c>
       <c r="M8">
-        <v>2.680889399999999</v>
+        <v>3.1277043</v>
       </c>
       <c r="N8">
-        <v>86.0191106</v>
+        <v>85.5722957</v>
       </c>
       <c r="O8">
-        <v>20.644586544</v>
+        <v>20.537350968</v>
       </c>
       <c r="P8">
-        <v>65.37452405600001</v>
+        <v>65.034944732</v>
       </c>
       <c r="Q8">
-        <v>97.774524056</v>
+        <v>97.43494473199999</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.08656071370009458</v>
+        <v>0.08689867870162274</v>
       </c>
       <c r="T8">
-        <v>0.8380831750684475</v>
+        <v>0.8450320912141938</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>33.08603480621021</v>
+        <v>28.35945840532304</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08349173119250915</v>
+        <v>0.08332271150692939</v>
       </c>
       <c r="C9">
-        <v>789.6194197538387</v>
+        <v>782.4517727280416</v>
       </c>
       <c r="D9">
-        <v>558.2004197538387</v>
+        <v>559.9157727280416</v>
       </c>
       <c r="E9">
-        <v>-339.919</v>
+        <v>-331.0360000000001</v>
       </c>
       <c r="F9">
-        <v>62.181</v>
+        <v>71.06399999999999</v>
       </c>
       <c r="G9">
         <v>293.6</v>
@@ -2025,28 +2025,28 @@
         <v>88.7</v>
       </c>
       <c r="M9">
-        <v>3.1277043</v>
+        <v>3.5745192</v>
       </c>
       <c r="N9">
-        <v>85.5722957</v>
+        <v>85.12548080000001</v>
       </c>
       <c r="O9">
-        <v>20.537350968</v>
+        <v>20.430115392</v>
       </c>
       <c r="P9">
-        <v>65.034944732</v>
+        <v>64.695365408</v>
       </c>
       <c r="Q9">
-        <v>97.43494473199999</v>
+        <v>97.09536540799999</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.08689867870162274</v>
+        <v>0.0872439907684015</v>
       </c>
       <c r="T9">
-        <v>0.8450320912141938</v>
+        <v>0.8521320707544128</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>28.35945840532304</v>
+        <v>24.81452610465766</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08332271150692939</v>
+        <v>0.08315369182134962</v>
       </c>
       <c r="C10">
-        <v>782.4517727280416</v>
+        <v>775.2947007778461</v>
       </c>
       <c r="D10">
-        <v>559.9157727280416</v>
+        <v>561.641700777846</v>
       </c>
       <c r="E10">
-        <v>-331.0360000000001</v>
+        <v>-322.153</v>
       </c>
       <c r="F10">
-        <v>71.06399999999999</v>
+        <v>79.94699999999999</v>
       </c>
       <c r="G10">
         <v>293.6</v>
@@ -2107,28 +2107,28 @@
         <v>88.7</v>
       </c>
       <c r="M10">
-        <v>3.5745192</v>
+        <v>4.021334099999999</v>
       </c>
       <c r="N10">
-        <v>85.12548080000001</v>
+        <v>84.6786659</v>
       </c>
       <c r="O10">
-        <v>20.430115392</v>
+        <v>20.322879816</v>
       </c>
       <c r="P10">
-        <v>64.695365408</v>
+        <v>64.355786084</v>
       </c>
       <c r="Q10">
-        <v>97.09536540799999</v>
+        <v>96.75578608399999</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.0872439907684015</v>
+        <v>0.0875968921113732</v>
       </c>
       <c r="T10">
-        <v>0.8521320707544128</v>
+        <v>0.8593880938010102</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>24.81452610465766</v>
+        <v>22.05735653747348</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08315369182134962</v>
+        <v>0.08298467213576988</v>
       </c>
       <c r="C11">
-        <v>775.2947007778461</v>
+        <v>768.1483019979396</v>
       </c>
       <c r="D11">
-        <v>561.641700777846</v>
+        <v>563.3783019979396</v>
       </c>
       <c r="E11">
-        <v>-322.153</v>
+        <v>-313.27</v>
       </c>
       <c r="F11">
-        <v>79.94699999999999</v>
+        <v>88.82999999999998</v>
       </c>
       <c r="G11">
         <v>293.6</v>
@@ -2189,28 +2189,28 @@
         <v>88.7</v>
       </c>
       <c r="M11">
-        <v>4.021334099999999</v>
+        <v>4.468148999999999</v>
       </c>
       <c r="N11">
-        <v>84.6786659</v>
+        <v>84.23185100000001</v>
       </c>
       <c r="O11">
-        <v>20.322879816</v>
+        <v>20.21564424</v>
       </c>
       <c r="P11">
-        <v>64.355786084</v>
+        <v>64.01620676</v>
       </c>
       <c r="Q11">
-        <v>96.75578608399999</v>
+        <v>96.41620675999999</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.0875968921113732</v>
+        <v>0.08795763570641096</v>
       </c>
       <c r="T11">
-        <v>0.8593880938010102</v>
+        <v>0.8668053618041989</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>22.05735653747348</v>
+        <v>19.85162088372613</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08298467213576988</v>
+        <v>0.08281565245019011</v>
       </c>
       <c r="C12">
-        <v>768.1483019979396</v>
+        <v>761.0126757000132</v>
       </c>
       <c r="D12">
-        <v>563.3783019979396</v>
+        <v>565.1256757000132</v>
       </c>
       <c r="E12">
-        <v>-313.27</v>
+        <v>-304.3870000000001</v>
       </c>
       <c r="F12">
-        <v>88.83</v>
+        <v>97.71299999999999</v>
       </c>
       <c r="G12">
         <v>293.6</v>
@@ -2271,28 +2271,28 @@
         <v>88.7</v>
       </c>
       <c r="M12">
-        <v>4.468148999999999</v>
+        <v>4.914963899999999</v>
       </c>
       <c r="N12">
-        <v>84.23185100000001</v>
+        <v>83.7850361</v>
       </c>
       <c r="O12">
-        <v>20.21564424</v>
+        <v>20.108408664</v>
       </c>
       <c r="P12">
-        <v>64.01620676</v>
+        <v>63.676627436</v>
       </c>
       <c r="Q12">
-        <v>96.41620675999999</v>
+        <v>96.076627436</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.08795763570641096</v>
+        <v>0.08832648589909001</v>
       </c>
       <c r="T12">
-        <v>0.8668053618041989</v>
+        <v>0.8743893099872343</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>19.85162088372613</v>
+        <v>18.04692807611466</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08281565245019011</v>
+        <v>0.08264663276461032</v>
       </c>
       <c r="C13">
-        <v>761.0126757000132</v>
+        <v>753.8879224316902</v>
       </c>
       <c r="D13">
-        <v>565.1256757000132</v>
+        <v>566.8839224316902</v>
       </c>
       <c r="E13">
-        <v>-304.3870000000001</v>
+        <v>-295.504</v>
       </c>
       <c r="F13">
-        <v>97.71299999999999</v>
+        <v>106.596</v>
       </c>
       <c r="G13">
         <v>293.6</v>
@@ -2353,28 +2353,28 @@
         <v>88.7</v>
       </c>
       <c r="M13">
-        <v>4.914963899999999</v>
+        <v>5.361778799999999</v>
       </c>
       <c r="N13">
-        <v>83.7850361</v>
+        <v>83.33822120000001</v>
       </c>
       <c r="O13">
-        <v>20.108408664</v>
+        <v>20.001173088</v>
       </c>
       <c r="P13">
-        <v>63.676627436</v>
+        <v>63.33704811200001</v>
       </c>
       <c r="Q13">
-        <v>96.076627436</v>
+        <v>95.737048112</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.08832648589909001</v>
+        <v>0.08870371905069355</v>
       </c>
       <c r="T13">
-        <v>0.8743893099872343</v>
+        <v>0.8821456206289749</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>18.04692807611466</v>
+        <v>16.54301740310511</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08264663276461032</v>
+        <v>0.08247761307903058</v>
       </c>
       <c r="C14">
-        <v>753.8879224316902</v>
+        <v>746.7741439958133</v>
       </c>
       <c r="D14">
-        <v>566.8839224316902</v>
+        <v>568.6531439958134</v>
       </c>
       <c r="E14">
-        <v>-295.504</v>
+        <v>-286.621</v>
       </c>
       <c r="F14">
-        <v>106.596</v>
+        <v>115.479</v>
       </c>
       <c r="G14">
         <v>293.6</v>
@@ -2435,28 +2435,28 @@
         <v>88.7</v>
       </c>
       <c r="M14">
-        <v>5.361778799999999</v>
+        <v>5.808593699999999</v>
       </c>
       <c r="N14">
-        <v>83.33822120000001</v>
+        <v>82.8914063</v>
       </c>
       <c r="O14">
-        <v>20.001173088</v>
+        <v>19.893937512</v>
       </c>
       <c r="P14">
-        <v>63.33704811200001</v>
+        <v>62.997468788</v>
       </c>
       <c r="Q14">
-        <v>95.737048112</v>
+        <v>95.397468788</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.08870371905069355</v>
+        <v>0.08908962422877079</v>
       </c>
       <c r="T14">
-        <v>0.8821456206289749</v>
+        <v>0.8900802372624801</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>16.54301740310511</v>
+        <v>15.27047760286625</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08247761307903058</v>
+        <v>0.08230859339345081</v>
       </c>
       <c r="C15">
-        <v>746.7741439958133</v>
+        <v>739.6714434700962</v>
       </c>
       <c r="D15">
-        <v>568.6531439958134</v>
+        <v>570.4334434700961</v>
       </c>
       <c r="E15">
-        <v>-286.621</v>
+        <v>-277.738</v>
       </c>
       <c r="F15">
-        <v>115.479</v>
+        <v>124.362</v>
       </c>
       <c r="G15">
         <v>293.6</v>
@@ -2517,28 +2517,28 @@
         <v>88.7</v>
       </c>
       <c r="M15">
-        <v>5.808593699999999</v>
+        <v>6.2554086</v>
       </c>
       <c r="N15">
-        <v>82.8914063</v>
+        <v>82.44459140000001</v>
       </c>
       <c r="O15">
-        <v>19.893937512</v>
+        <v>19.786701936</v>
       </c>
       <c r="P15">
-        <v>62.997468788</v>
+        <v>62.65788946400001</v>
       </c>
       <c r="Q15">
-        <v>95.397468788</v>
+        <v>95.057889464</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.08908962422877079</v>
+        <v>0.08948450394587304</v>
       </c>
       <c r="T15">
-        <v>0.8900802372624801</v>
+        <v>0.8981993798642061</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>15.27047760286625</v>
+        <v>14.17972920266152</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08230859339345081</v>
+        <v>0.08213957370787105</v>
       </c>
       <c r="C16">
-        <v>739.6714434700962</v>
+        <v>732.5799252271387</v>
       </c>
       <c r="D16">
-        <v>570.4334434700961</v>
+        <v>572.2249252271387</v>
       </c>
       <c r="E16">
-        <v>-277.738</v>
+        <v>-268.855</v>
       </c>
       <c r="F16">
-        <v>124.362</v>
+        <v>133.245</v>
       </c>
       <c r="G16">
         <v>293.6</v>
@@ -2599,28 +2599,28 @@
         <v>88.7</v>
       </c>
       <c r="M16">
-        <v>6.2554086</v>
+        <v>6.7022235</v>
       </c>
       <c r="N16">
-        <v>82.44459140000001</v>
+        <v>81.9977765</v>
       </c>
       <c r="O16">
-        <v>19.786701936</v>
+        <v>19.67946636</v>
       </c>
       <c r="P16">
-        <v>62.65788946400001</v>
+        <v>62.31831014</v>
       </c>
       <c r="Q16">
-        <v>95.057889464</v>
+        <v>94.71831014</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.08948450394587304</v>
+        <v>0.08988867495043654</v>
       </c>
       <c r="T16">
-        <v>0.8981993798642061</v>
+        <v>0.9065095611153845</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>14.17972920266152</v>
+        <v>13.23441392248408</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08213957370787105</v>
+        <v>0.08215295402229128</v>
       </c>
       <c r="C17">
-        <v>732.5799252271387</v>
+        <v>723.554693904026</v>
       </c>
       <c r="D17">
-        <v>572.2249252271387</v>
+        <v>572.082693904026</v>
       </c>
       <c r="E17">
-        <v>-268.855</v>
+        <v>-259.972</v>
       </c>
       <c r="F17">
-        <v>133.245</v>
+        <v>142.128</v>
       </c>
       <c r="G17">
         <v>293.6</v>
@@ -2681,45 +2681,45 @@
         <v>88.7</v>
       </c>
       <c r="M17">
-        <v>6.702223499999999</v>
+        <v>7.362230399999999</v>
       </c>
       <c r="N17">
-        <v>81.9977765</v>
+        <v>81.3377696</v>
       </c>
       <c r="O17">
-        <v>19.67946636</v>
+        <v>19.521064704</v>
       </c>
       <c r="P17">
-        <v>62.31831014</v>
+        <v>61.816704896</v>
       </c>
       <c r="Q17">
-        <v>94.71831014</v>
+        <v>94.216704896</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.08988867495043654</v>
+        <v>0.09030246907415629</v>
       </c>
       <c r="T17">
-        <v>0.9065095611153844</v>
+        <v>0.9150176038249243</v>
       </c>
       <c r="U17">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V17">
         <v>0.24</v>
       </c>
       <c r="W17">
-        <v>0.038228</v>
+        <v>0.039368</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y17">
-        <v>13.23441392248409</v>
+        <v>12.04797937320734</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08215295402229128</v>
+        <v>0.08199533433671151</v>
       </c>
       <c r="C18">
-        <v>723.554693904026</v>
+        <v>716.3516769971046</v>
       </c>
       <c r="D18">
-        <v>572.082693904026</v>
+        <v>573.7626769971046</v>
       </c>
       <c r="E18">
-        <v>-259.972</v>
+        <v>-251.089</v>
       </c>
       <c r="F18">
-        <v>142.128</v>
+        <v>151.011</v>
       </c>
       <c r="G18">
         <v>293.6</v>
@@ -2763,28 +2763,28 @@
         <v>88.7</v>
       </c>
       <c r="M18">
-        <v>7.362230399999999</v>
+        <v>7.8223698</v>
       </c>
       <c r="N18">
-        <v>81.3377696</v>
+        <v>80.8776302</v>
       </c>
       <c r="O18">
-        <v>19.521064704</v>
+        <v>19.410631248</v>
       </c>
       <c r="P18">
-        <v>61.816704896</v>
+        <v>61.466998952</v>
       </c>
       <c r="Q18">
-        <v>94.216704896</v>
+        <v>93.86699895199999</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09030246907415629</v>
+        <v>0.09072623414061629</v>
       </c>
       <c r="T18">
-        <v>0.9150176038249243</v>
+        <v>0.9237306596118022</v>
       </c>
       <c r="U18">
         <v>0.0518</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>12.04797937320734</v>
+        <v>11.33927470419514</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08199533433671151</v>
+        <v>0.08183771465113177</v>
       </c>
       <c r="C19">
-        <v>716.3516769971046</v>
+        <v>709.1585560571533</v>
       </c>
       <c r="D19">
-        <v>573.7626769971046</v>
+        <v>575.4525560571533</v>
       </c>
       <c r="E19">
-        <v>-251.089</v>
+        <v>-242.206</v>
       </c>
       <c r="F19">
-        <v>151.011</v>
+        <v>159.894</v>
       </c>
       <c r="G19">
         <v>293.6</v>
@@ -2845,28 +2845,28 @@
         <v>88.7</v>
       </c>
       <c r="M19">
-        <v>7.8223698</v>
+        <v>8.2825092</v>
       </c>
       <c r="N19">
-        <v>80.8776302</v>
+        <v>80.4174908</v>
       </c>
       <c r="O19">
-        <v>19.410631248</v>
+        <v>19.300197792</v>
       </c>
       <c r="P19">
-        <v>61.466998952</v>
+        <v>61.117293008</v>
       </c>
       <c r="Q19">
-        <v>93.86699895199999</v>
+        <v>93.517293008</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09072623414061629</v>
+        <v>0.0911603349404046</v>
       </c>
       <c r="T19">
-        <v>0.9237306596118022</v>
+        <v>0.932656228954458</v>
       </c>
       <c r="U19">
         <v>0.0518</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>11.33927470419514</v>
+        <v>10.70931499840652</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08183771465113175</v>
+        <v>0.08168009496555199</v>
       </c>
       <c r="C20">
-        <v>709.1585560571534</v>
+        <v>701.9754187809874</v>
       </c>
       <c r="D20">
-        <v>575.4525560571534</v>
+        <v>577.1524187809874</v>
       </c>
       <c r="E20">
-        <v>-242.206</v>
+        <v>-233.323</v>
       </c>
       <c r="F20">
-        <v>159.894</v>
+        <v>168.777</v>
       </c>
       <c r="G20">
         <v>293.6</v>
@@ -2927,28 +2927,28 @@
         <v>88.7</v>
       </c>
       <c r="M20">
-        <v>8.282509199999998</v>
+        <v>8.742648599999999</v>
       </c>
       <c r="N20">
-        <v>80.41749080000001</v>
+        <v>79.95735140000001</v>
       </c>
       <c r="O20">
-        <v>19.300197792</v>
+        <v>19.189764336</v>
       </c>
       <c r="P20">
-        <v>61.117293008</v>
+        <v>60.76758706400001</v>
       </c>
       <c r="Q20">
-        <v>93.517293008</v>
+        <v>93.167587064</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09116033494040458</v>
+        <v>0.09160515427845925</v>
       </c>
       <c r="T20">
-        <v>0.9326562289544578</v>
+        <v>0.9418021827253271</v>
       </c>
       <c r="U20">
         <v>0.0518</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>10.70931499840652</v>
+        <v>10.14566684059565</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08168009496555199</v>
+        <v>0.08178087527997224</v>
       </c>
       <c r="C21">
-        <v>701.9754187809874</v>
+        <v>692.0043894371306</v>
       </c>
       <c r="D21">
-        <v>577.1524187809874</v>
+        <v>576.0643894371306</v>
       </c>
       <c r="E21">
-        <v>-233.323</v>
+        <v>-224.44</v>
       </c>
       <c r="F21">
-        <v>168.777</v>
+        <v>177.66</v>
       </c>
       <c r="G21">
         <v>293.6</v>
@@ -3009,45 +3009,45 @@
         <v>88.7</v>
       </c>
       <c r="M21">
-        <v>8.742648599999999</v>
+        <v>9.504809999999999</v>
       </c>
       <c r="N21">
-        <v>79.95735140000001</v>
+        <v>79.19519</v>
       </c>
       <c r="O21">
-        <v>19.189764336</v>
+        <v>19.0068456</v>
       </c>
       <c r="P21">
-        <v>60.76758706400001</v>
+        <v>60.1883444</v>
       </c>
       <c r="Q21">
-        <v>93.167587064</v>
+        <v>92.58834439999998</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09160515427845925</v>
+        <v>0.0920610940999653</v>
       </c>
       <c r="T21">
-        <v>0.9418021827253271</v>
+        <v>0.9511767853404681</v>
       </c>
       <c r="U21">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V21">
         <v>0.24</v>
       </c>
       <c r="W21">
-        <v>0.039368</v>
+        <v>0.04066</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y21">
-        <v>10.14566684059565</v>
+        <v>9.332117107022656</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08178087527997224</v>
+        <v>0.08163617559439248</v>
       </c>
       <c r="C22">
-        <v>692.0043894371306</v>
+        <v>684.6848614072446</v>
       </c>
       <c r="D22">
-        <v>576.0643894371306</v>
+        <v>577.6278614072446</v>
       </c>
       <c r="E22">
-        <v>-224.44</v>
+        <v>-215.557</v>
       </c>
       <c r="F22">
-        <v>177.66</v>
+        <v>186.543</v>
       </c>
       <c r="G22">
         <v>293.6</v>
@@ -3091,28 +3091,28 @@
         <v>88.7</v>
       </c>
       <c r="M22">
-        <v>9.504809999999999</v>
+        <v>9.980050500000001</v>
       </c>
       <c r="N22">
-        <v>79.19519</v>
+        <v>78.7199495</v>
       </c>
       <c r="O22">
-        <v>19.0068456</v>
+        <v>18.89278788</v>
       </c>
       <c r="P22">
-        <v>60.1883444</v>
+        <v>59.82716162</v>
       </c>
       <c r="Q22">
-        <v>92.58834439999998</v>
+        <v>92.22716161999999</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.0920610940999653</v>
+        <v>0.09252857670176262</v>
       </c>
       <c r="T22">
-        <v>0.9511767853404681</v>
+        <v>0.960788719667385</v>
       </c>
       <c r="U22">
         <v>0.0535</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>9.332117107022656</v>
+        <v>8.887730578116813</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08163617559439248</v>
+        <v>0.08149147590881271</v>
       </c>
       <c r="C23">
-        <v>684.6848614072446</v>
+        <v>677.3738431796135</v>
       </c>
       <c r="D23">
-        <v>577.6278614072446</v>
+        <v>579.1998431796134</v>
       </c>
       <c r="E23">
-        <v>-215.557</v>
+        <v>-206.674</v>
       </c>
       <c r="F23">
-        <v>186.543</v>
+        <v>195.426</v>
       </c>
       <c r="G23">
         <v>293.6</v>
@@ -3173,28 +3173,28 @@
         <v>88.7</v>
       </c>
       <c r="M23">
-        <v>9.980050499999999</v>
+        <v>10.455291</v>
       </c>
       <c r="N23">
-        <v>78.7199495</v>
+        <v>78.244709</v>
       </c>
       <c r="O23">
-        <v>18.89278788</v>
+        <v>18.77873016</v>
       </c>
       <c r="P23">
-        <v>59.82716162</v>
+        <v>59.46597884000001</v>
       </c>
       <c r="Q23">
-        <v>92.22716161999999</v>
+        <v>91.86597884</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.09252857670176262</v>
+        <v>0.09300804603693938</v>
       </c>
       <c r="T23">
-        <v>0.960788719667385</v>
+        <v>0.9706471138488381</v>
       </c>
       <c r="U23">
         <v>0.0535</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>8.887730578116814</v>
+        <v>8.48374282456605</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08149147590881271</v>
+        <v>0.08134677622323297</v>
       </c>
       <c r="C24">
-        <v>677.3738431796135</v>
+        <v>670.0714044206758</v>
       </c>
       <c r="D24">
-        <v>579.1998431796134</v>
+        <v>580.7804044206757</v>
       </c>
       <c r="E24">
-        <v>-206.674</v>
+        <v>-197.791</v>
       </c>
       <c r="F24">
-        <v>195.426</v>
+        <v>204.309</v>
       </c>
       <c r="G24">
         <v>293.6</v>
@@ -3255,28 +3255,28 @@
         <v>88.7</v>
       </c>
       <c r="M24">
-        <v>10.455291</v>
+        <v>10.9305315</v>
       </c>
       <c r="N24">
-        <v>78.244709</v>
+        <v>77.7694685</v>
       </c>
       <c r="O24">
-        <v>18.77873016</v>
+        <v>18.66467244</v>
       </c>
       <c r="P24">
-        <v>59.46597884000001</v>
+        <v>59.10479606</v>
       </c>
       <c r="Q24">
-        <v>91.86597884</v>
+        <v>91.50479605999999</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09300804603693938</v>
+        <v>0.09349996912108176</v>
       </c>
       <c r="T24">
-        <v>0.9706471138488381</v>
+        <v>0.9807615702168224</v>
       </c>
       <c r="U24">
         <v>0.0535</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>8.48374282456605</v>
+        <v>8.114884440889266</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08134677622323297</v>
+        <v>0.08120207653765318</v>
       </c>
       <c r="C25">
-        <v>670.0714044206758</v>
+        <v>662.7776155593957</v>
       </c>
       <c r="D25">
-        <v>580.7804044206757</v>
+        <v>582.3696155593957</v>
       </c>
       <c r="E25">
-        <v>-197.791</v>
+        <v>-188.908</v>
       </c>
       <c r="F25">
-        <v>204.309</v>
+        <v>213.192</v>
       </c>
       <c r="G25">
         <v>293.6</v>
@@ -3337,28 +3337,28 @@
         <v>88.7</v>
       </c>
       <c r="M25">
-        <v>10.9305315</v>
+        <v>11.405772</v>
       </c>
       <c r="N25">
-        <v>77.7694685</v>
+        <v>77.294228</v>
       </c>
       <c r="O25">
-        <v>18.66467244</v>
+        <v>18.55061472</v>
       </c>
       <c r="P25">
-        <v>59.10479606</v>
+        <v>58.74361328000001</v>
       </c>
       <c r="Q25">
-        <v>91.50479605999999</v>
+        <v>91.14361328</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09349996912108176</v>
+        <v>0.09400483754954367</v>
       </c>
       <c r="T25">
-        <v>0.9807615702168224</v>
+        <v>0.9911421964892273</v>
       </c>
       <c r="U25">
         <v>0.0535</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>8.114884440889266</v>
+        <v>7.776764255852212</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08120207653765318</v>
+        <v>0.08120937685207344</v>
       </c>
       <c r="C26">
-        <v>662.7776155593957</v>
+        <v>653.8142291963152</v>
       </c>
       <c r="D26">
-        <v>582.3696155593957</v>
+        <v>582.2892291963152</v>
       </c>
       <c r="E26">
-        <v>-188.908</v>
+        <v>-180.025</v>
       </c>
       <c r="F26">
-        <v>213.192</v>
+        <v>222.075</v>
       </c>
       <c r="G26">
         <v>293.6</v>
@@ -3419,45 +3419,45 @@
         <v>88.7</v>
       </c>
       <c r="M26">
-        <v>11.405772</v>
+        <v>12.0586725</v>
       </c>
       <c r="N26">
-        <v>77.294228</v>
+        <v>76.6413275</v>
       </c>
       <c r="O26">
-        <v>18.55061472</v>
+        <v>18.3939186</v>
       </c>
       <c r="P26">
-        <v>58.74361328000001</v>
+        <v>58.2474089</v>
       </c>
       <c r="Q26">
-        <v>91.14361328</v>
+        <v>90.64740889999999</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.09400483754954367</v>
+        <v>0.09452316913609791</v>
       </c>
       <c r="T26">
-        <v>0.9911421964892273</v>
+        <v>1.00179963946223</v>
       </c>
       <c r="U26">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V26">
         <v>0.24</v>
       </c>
       <c r="W26">
-        <v>0.04066</v>
+        <v>0.041268</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y26">
-        <v>7.776764255852213</v>
+        <v>7.355701881778447</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08120937685207344</v>
+        <v>0.08107075716649367</v>
       </c>
       <c r="C27">
-        <v>653.8142291963152</v>
+        <v>646.4614198795551</v>
       </c>
       <c r="D27">
-        <v>582.2892291963152</v>
+        <v>583.8194198795551</v>
       </c>
       <c r="E27">
-        <v>-180.025</v>
+        <v>-171.142</v>
       </c>
       <c r="F27">
-        <v>222.075</v>
+        <v>230.958</v>
       </c>
       <c r="G27">
         <v>293.6</v>
@@ -3501,28 +3501,28 @@
         <v>88.7</v>
       </c>
       <c r="M27">
-        <v>12.0586725</v>
+        <v>12.5410194</v>
       </c>
       <c r="N27">
-        <v>76.6413275</v>
+        <v>76.15898060000001</v>
       </c>
       <c r="O27">
-        <v>18.3939186</v>
+        <v>18.278155344</v>
       </c>
       <c r="P27">
-        <v>58.2474089</v>
+        <v>57.88082525600001</v>
       </c>
       <c r="Q27">
-        <v>90.64740889999999</v>
+        <v>90.280825256</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.09452316913609791</v>
+        <v>0.0950555096844509</v>
       </c>
       <c r="T27">
-        <v>1.00179963946223</v>
+        <v>1.012745121434502</v>
       </c>
       <c r="U27">
         <v>0.0543</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>7.355701881778447</v>
+        <v>7.072790270940814</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08107075716649367</v>
+        <v>0.08093213748091391</v>
       </c>
       <c r="C28">
-        <v>646.4614198795551</v>
+        <v>639.1166740912871</v>
       </c>
       <c r="D28">
-        <v>583.8194198795551</v>
+        <v>585.3576740912871</v>
       </c>
       <c r="E28">
-        <v>-171.142</v>
+        <v>-162.259</v>
       </c>
       <c r="F28">
-        <v>230.958</v>
+        <v>239.841</v>
       </c>
       <c r="G28">
         <v>293.6</v>
@@ -3583,28 +3583,28 @@
         <v>88.7</v>
       </c>
       <c r="M28">
-        <v>12.5410194</v>
+        <v>13.0233663</v>
       </c>
       <c r="N28">
-        <v>76.15898060000001</v>
+        <v>75.6766337</v>
       </c>
       <c r="O28">
-        <v>18.278155344</v>
+        <v>18.162392088</v>
       </c>
       <c r="P28">
-        <v>57.88082525600001</v>
+        <v>57.514241612</v>
       </c>
       <c r="Q28">
-        <v>90.280825256</v>
+        <v>89.91424161199998</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.0950555096844509</v>
+        <v>0.09560243490536152</v>
       </c>
       <c r="T28">
-        <v>1.012745121434502</v>
+        <v>1.023990479625194</v>
       </c>
       <c r="U28">
         <v>0.0543</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>7.072790270940814</v>
+        <v>6.810835075720783</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08093213748091391</v>
+        <v>0.08079351779533415</v>
       </c>
       <c r="C29">
-        <v>639.1166740912871</v>
+        <v>631.780055737528</v>
       </c>
       <c r="D29">
-        <v>585.3576740912871</v>
+        <v>586.904055737528</v>
       </c>
       <c r="E29">
-        <v>-162.259</v>
+        <v>-153.376</v>
       </c>
       <c r="F29">
-        <v>239.841</v>
+        <v>248.724</v>
       </c>
       <c r="G29">
         <v>293.6</v>
@@ -3665,28 +3665,28 @@
         <v>88.7</v>
       </c>
       <c r="M29">
-        <v>13.0233663</v>
+        <v>13.5057132</v>
       </c>
       <c r="N29">
-        <v>75.6766337</v>
+        <v>75.1942868</v>
       </c>
       <c r="O29">
-        <v>18.162392088</v>
+        <v>18.046628832</v>
       </c>
       <c r="P29">
-        <v>57.514241612</v>
+        <v>57.147657968</v>
       </c>
       <c r="Q29">
-        <v>89.91424161199998</v>
+        <v>89.547657968</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.09560243490536152</v>
+        <v>0.09616455249351966</v>
       </c>
       <c r="T29">
-        <v>1.023990479625194</v>
+        <v>1.035548208876738</v>
       </c>
       <c r="U29">
         <v>0.0543</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>6.810835075720783</v>
+        <v>6.567590965873612</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.08079351779533415</v>
+        <v>0.08065489810975439</v>
       </c>
       <c r="C30">
-        <v>631.780055737528</v>
+        <v>624.4516294013843</v>
       </c>
       <c r="D30">
-        <v>586.904055737528</v>
+        <v>588.4586294013843</v>
       </c>
       <c r="E30">
-        <v>-153.376</v>
+        <v>-144.493</v>
       </c>
       <c r="F30">
-        <v>248.724</v>
+        <v>257.607</v>
       </c>
       <c r="G30">
         <v>293.6</v>
@@ -3747,28 +3747,28 @@
         <v>88.7</v>
       </c>
       <c r="M30">
-        <v>13.5057132</v>
+        <v>13.9880601</v>
       </c>
       <c r="N30">
-        <v>75.1942868</v>
+        <v>74.7119399</v>
       </c>
       <c r="O30">
-        <v>18.046628832</v>
+        <v>17.930865576</v>
       </c>
       <c r="P30">
-        <v>57.147657968</v>
+        <v>56.781074324</v>
       </c>
       <c r="Q30">
-        <v>89.547657968</v>
+        <v>89.18107432399999</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.09616455249351966</v>
+        <v>0.09674250437993576</v>
       </c>
       <c r="T30">
-        <v>1.035548208876738</v>
+        <v>1.047431507966353</v>
       </c>
       <c r="U30">
         <v>0.0543</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>6.567590965873612</v>
+        <v>6.34112231187797</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.08065489810975439</v>
+        <v>0.08051627842417462</v>
       </c>
       <c r="C31">
-        <v>624.4516294013844</v>
+        <v>617.1314603520423</v>
       </c>
       <c r="D31">
-        <v>588.4586294013843</v>
+        <v>590.0214603520423</v>
       </c>
       <c r="E31">
-        <v>-144.4930000000001</v>
+        <v>-135.6100000000001</v>
       </c>
       <c r="F31">
-        <v>257.607</v>
+        <v>266.49</v>
       </c>
       <c r="G31">
         <v>293.6</v>
@@ -3829,28 +3829,28 @@
         <v>88.7</v>
       </c>
       <c r="M31">
-        <v>13.9880601</v>
+        <v>14.470407</v>
       </c>
       <c r="N31">
-        <v>74.7119399</v>
+        <v>74.22959300000001</v>
       </c>
       <c r="O31">
-        <v>17.930865576</v>
+        <v>17.81510232</v>
       </c>
       <c r="P31">
-        <v>56.781074324</v>
+        <v>56.41449068000001</v>
       </c>
       <c r="Q31">
-        <v>89.18107432399999</v>
+        <v>88.81449068000001</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.09674250437993576</v>
+        <v>0.09733696917739232</v>
       </c>
       <c r="T31">
-        <v>1.047431507966353</v>
+        <v>1.0596543298871</v>
       </c>
       <c r="U31">
         <v>0.0543</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>6.341122311877972</v>
+        <v>6.129751568148706</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.08051627842417462</v>
+        <v>0.08061325873859485</v>
       </c>
       <c r="C32">
-        <v>617.1314603520423</v>
+        <v>607.1542108266431</v>
       </c>
       <c r="D32">
-        <v>590.0214603520423</v>
+        <v>588.927210826643</v>
       </c>
       <c r="E32">
-        <v>-135.6100000000001</v>
+        <v>-126.727</v>
       </c>
       <c r="F32">
-        <v>266.49</v>
+        <v>275.373</v>
       </c>
       <c r="G32">
         <v>293.6</v>
@@ -3911,45 +3911,45 @@
         <v>88.7</v>
       </c>
       <c r="M32">
-        <v>14.470407</v>
+        <v>15.2281269</v>
       </c>
       <c r="N32">
-        <v>74.22959300000001</v>
+        <v>73.47187310000001</v>
       </c>
       <c r="O32">
-        <v>17.81510232</v>
+        <v>17.633249544</v>
       </c>
       <c r="P32">
-        <v>56.41449068000001</v>
+        <v>55.83862355600001</v>
       </c>
       <c r="Q32">
-        <v>88.81449068000001</v>
+        <v>88.23862355599999</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.09733696917739232</v>
+        <v>0.09794866483854327</v>
       </c>
       <c r="T32">
-        <v>1.0596543298871</v>
+        <v>1.072231436501202</v>
       </c>
       <c r="U32">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V32">
         <v>0.24</v>
       </c>
       <c r="W32">
-        <v>0.041268</v>
+        <v>0.042028</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y32">
-        <v>6.129751568148706</v>
+        <v>5.824747888067574</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08061325873859485</v>
+        <v>0.08048223905301509</v>
       </c>
       <c r="C33">
-        <v>607.1542108266431</v>
+        <v>599.7504985495614</v>
       </c>
       <c r="D33">
-        <v>588.927210826643</v>
+        <v>590.4064985495613</v>
       </c>
       <c r="E33">
-        <v>-126.727</v>
+        <v>-117.8440000000001</v>
       </c>
       <c r="F33">
-        <v>275.373</v>
+        <v>284.256</v>
       </c>
       <c r="G33">
         <v>293.6</v>
@@ -3993,28 +3993,28 @@
         <v>88.7</v>
       </c>
       <c r="M33">
-        <v>15.2281269</v>
+        <v>15.7193568</v>
       </c>
       <c r="N33">
-        <v>73.47187310000001</v>
+        <v>72.9806432</v>
       </c>
       <c r="O33">
-        <v>17.633249544</v>
+        <v>17.515354368</v>
       </c>
       <c r="P33">
-        <v>55.83862355600001</v>
+        <v>55.465288832</v>
       </c>
       <c r="Q33">
-        <v>88.23862355599999</v>
+        <v>87.86528883199999</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.09794866483854327</v>
+        <v>0.09857835154855162</v>
       </c>
       <c r="T33">
-        <v>1.072231436501202</v>
+        <v>1.08517845801572</v>
       </c>
       <c r="U33">
         <v>0.0553</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>5.824747888067574</v>
+        <v>5.642724516565462</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08048223905301509</v>
+        <v>0.08035121936743532</v>
       </c>
       <c r="C34">
-        <v>599.7504985495614</v>
+        <v>592.3542364381238</v>
       </c>
       <c r="D34">
-        <v>590.4064985495613</v>
+        <v>591.8932364381238</v>
       </c>
       <c r="E34">
-        <v>-117.8440000000001</v>
+        <v>-108.961</v>
       </c>
       <c r="F34">
-        <v>284.256</v>
+        <v>293.139</v>
       </c>
       <c r="G34">
         <v>293.6</v>
@@ -4075,28 +4075,28 @@
         <v>88.7</v>
       </c>
       <c r="M34">
-        <v>15.7193568</v>
+        <v>16.2105867</v>
       </c>
       <c r="N34">
-        <v>72.9806432</v>
+        <v>72.4894133</v>
       </c>
       <c r="O34">
-        <v>17.515354368</v>
+        <v>17.397459192</v>
       </c>
       <c r="P34">
-        <v>55.465288832</v>
+        <v>55.091954108</v>
       </c>
       <c r="Q34">
-        <v>87.86528883199999</v>
+        <v>87.49195410799999</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.09857835154855162</v>
+        <v>0.09922683487676914</v>
       </c>
       <c r="T34">
-        <v>1.08517845801572</v>
+        <v>1.098511957784401</v>
       </c>
       <c r="U34">
         <v>0.0553</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>5.642724516565462</v>
+        <v>5.471732864548326</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.08035121936743532</v>
+        <v>0.08022019968185556</v>
       </c>
       <c r="C35">
-        <v>592.3542364381238</v>
+        <v>584.9654809165374</v>
       </c>
       <c r="D35">
-        <v>591.8932364381238</v>
+        <v>593.3874809165375</v>
       </c>
       <c r="E35">
-        <v>-108.961</v>
+        <v>-100.078</v>
       </c>
       <c r="F35">
-        <v>293.139</v>
+        <v>302.022</v>
       </c>
       <c r="G35">
         <v>293.6</v>
@@ -4157,28 +4157,28 @@
         <v>88.7</v>
       </c>
       <c r="M35">
-        <v>16.2105867</v>
+        <v>16.7018166</v>
       </c>
       <c r="N35">
-        <v>72.4894133</v>
+        <v>71.9981834</v>
       </c>
       <c r="O35">
-        <v>17.397459192</v>
+        <v>17.279564016</v>
       </c>
       <c r="P35">
-        <v>55.091954108</v>
+        <v>54.71861938400001</v>
       </c>
       <c r="Q35">
-        <v>87.49195410799999</v>
+        <v>87.118619384</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.09922683487676914</v>
+        <v>0.09989496921493268</v>
       </c>
       <c r="T35">
-        <v>1.098511957784401</v>
+        <v>1.112249503000619</v>
       </c>
       <c r="U35">
         <v>0.0553</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>5.471732864548326</v>
+        <v>5.310799545002787</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.08022019968185556</v>
+        <v>0.08008917999627579</v>
       </c>
       <c r="C36">
-        <v>584.9654809165374</v>
+        <v>577.5842889802273</v>
       </c>
       <c r="D36">
-        <v>593.3874809165375</v>
+        <v>594.8892889802273</v>
       </c>
       <c r="E36">
-        <v>-100.078</v>
+        <v>-91.19499999999999</v>
       </c>
       <c r="F36">
-        <v>302.022</v>
+        <v>310.905</v>
       </c>
       <c r="G36">
         <v>293.6</v>
@@ -4239,28 +4239,28 @@
         <v>88.7</v>
       </c>
       <c r="M36">
-        <v>16.7018166</v>
+        <v>17.1930465</v>
       </c>
       <c r="N36">
-        <v>71.9981834</v>
+        <v>71.50695350000001</v>
       </c>
       <c r="O36">
-        <v>17.279564016</v>
+        <v>17.16166884</v>
       </c>
       <c r="P36">
-        <v>54.71861938400001</v>
+        <v>54.34528466</v>
       </c>
       <c r="Q36">
-        <v>87.118619384</v>
+        <v>86.74528466</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.09989496921493268</v>
+        <v>0.100583661532732</v>
       </c>
       <c r="T36">
-        <v>1.112249503000619</v>
+        <v>1.126409741915797</v>
       </c>
       <c r="U36">
         <v>0.0553</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>5.310799545002787</v>
+        <v>5.159062415145565</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.08008917999627579</v>
+        <v>0.07995816031069605</v>
       </c>
       <c r="C37">
-        <v>577.5842889802273</v>
+        <v>570.2107182030819</v>
       </c>
       <c r="D37">
-        <v>594.8892889802273</v>
+        <v>596.3987182030819</v>
       </c>
       <c r="E37">
-        <v>-91.19499999999999</v>
+        <v>-82.31200000000001</v>
       </c>
       <c r="F37">
-        <v>310.905</v>
+        <v>319.788</v>
       </c>
       <c r="G37">
         <v>293.6</v>
@@ -4321,28 +4321,28 @@
         <v>88.7</v>
       </c>
       <c r="M37">
-        <v>17.1930465</v>
+        <v>17.6842764</v>
       </c>
       <c r="N37">
-        <v>71.50695350000001</v>
+        <v>71.0157236</v>
       </c>
       <c r="O37">
-        <v>17.16166884</v>
+        <v>17.043773664</v>
       </c>
       <c r="P37">
-        <v>54.34528466</v>
+        <v>53.971949936</v>
       </c>
       <c r="Q37">
-        <v>86.74528466</v>
+        <v>86.37194993599999</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.100583661532732</v>
+        <v>0.1012938754854626</v>
       </c>
       <c r="T37">
-        <v>1.126409741915797</v>
+        <v>1.141012488297074</v>
       </c>
       <c r="U37">
         <v>0.0553</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>5.159062415145565</v>
+        <v>5.015755125835965</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.07995816031069605</v>
+        <v>0.07982714062511628</v>
       </c>
       <c r="C38">
-        <v>570.210718203082</v>
+        <v>562.8448267448125</v>
       </c>
       <c r="D38">
-        <v>596.3987182030819</v>
+        <v>597.9158267448125</v>
       </c>
       <c r="E38">
-        <v>-82.31200000000007</v>
+        <v>-73.42900000000003</v>
       </c>
       <c r="F38">
-        <v>319.788</v>
+        <v>328.671</v>
       </c>
       <c r="G38">
         <v>293.6</v>
@@ -4403,28 +4403,28 @@
         <v>88.7</v>
       </c>
       <c r="M38">
-        <v>17.6842764</v>
+        <v>18.1755063</v>
       </c>
       <c r="N38">
-        <v>71.0157236</v>
+        <v>70.52449370000001</v>
       </c>
       <c r="O38">
-        <v>17.043773664</v>
+        <v>16.925878488</v>
       </c>
       <c r="P38">
-        <v>53.971949936</v>
+        <v>53.59861521200001</v>
       </c>
       <c r="Q38">
-        <v>86.37194993599999</v>
+        <v>85.998615212</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1012938754854626</v>
+        <v>0.102026635912883</v>
       </c>
       <c r="T38">
-        <v>1.141012488297074</v>
+        <v>1.156078813928551</v>
       </c>
       <c r="U38">
         <v>0.0553</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>5.015755125835966</v>
+        <v>4.880194176489049</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.07982714062511628</v>
+        <v>0.07969612093953651</v>
       </c>
       <c r="C39">
-        <v>562.8448267448125</v>
+        <v>555.4866733584219</v>
       </c>
       <c r="D39">
-        <v>597.9158267448125</v>
+        <v>599.4406733584218</v>
       </c>
       <c r="E39">
-        <v>-73.42900000000003</v>
+        <v>-64.54600000000005</v>
       </c>
       <c r="F39">
-        <v>328.671</v>
+        <v>337.554</v>
       </c>
       <c r="G39">
         <v>293.6</v>
@@ -4485,28 +4485,28 @@
         <v>88.7</v>
       </c>
       <c r="M39">
-        <v>18.1755063</v>
+        <v>18.6667362</v>
       </c>
       <c r="N39">
-        <v>70.52449370000001</v>
+        <v>70.0332638</v>
       </c>
       <c r="O39">
-        <v>16.925878488</v>
+        <v>16.807983312</v>
       </c>
       <c r="P39">
-        <v>53.59861521200001</v>
+        <v>53.225280488</v>
       </c>
       <c r="Q39">
-        <v>85.998615212</v>
+        <v>85.62528048799999</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.102026635912883</v>
+        <v>0.102783033773446</v>
       </c>
       <c r="T39">
-        <v>1.156078813928551</v>
+        <v>1.171631150064269</v>
       </c>
       <c r="U39">
         <v>0.0553</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>4.880194176489049</v>
+        <v>4.751768013949862</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.07969612093953651</v>
+        <v>0.07956510125395677</v>
       </c>
       <c r="C40">
-        <v>555.4866733584219</v>
+        <v>548.1363173977884</v>
       </c>
       <c r="D40">
-        <v>599.4406733584218</v>
+        <v>600.9733173977884</v>
       </c>
       <c r="E40">
-        <v>-64.54600000000005</v>
+        <v>-55.66300000000001</v>
       </c>
       <c r="F40">
-        <v>337.554</v>
+        <v>346.437</v>
       </c>
       <c r="G40">
         <v>293.6</v>
@@ -4567,28 +4567,28 @@
         <v>88.7</v>
       </c>
       <c r="M40">
-        <v>18.6667362</v>
+        <v>19.1579661</v>
       </c>
       <c r="N40">
-        <v>70.0332638</v>
+        <v>69.54203390000001</v>
       </c>
       <c r="O40">
-        <v>16.807983312</v>
+        <v>16.690088136</v>
       </c>
       <c r="P40">
-        <v>53.225280488</v>
+        <v>52.85194576400001</v>
       </c>
       <c r="Q40">
-        <v>85.62528048799999</v>
+        <v>85.251945764</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.102783033773446</v>
+        <v>0.1035642315638635</v>
       </c>
       <c r="T40">
-        <v>1.171631150064269</v>
+        <v>1.187693398860174</v>
       </c>
       <c r="U40">
         <v>0.0553</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>4.751768013949862</v>
+        <v>4.629927808463968</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.07956510125395677</v>
+        <v>0.079434081568377</v>
       </c>
       <c r="C41">
-        <v>548.1363173977884</v>
+        <v>540.7938188253695</v>
       </c>
       <c r="D41">
-        <v>600.9733173977884</v>
+        <v>602.5138188253695</v>
       </c>
       <c r="E41">
-        <v>-55.66300000000001</v>
+        <v>-46.78000000000003</v>
       </c>
       <c r="F41">
-        <v>346.437</v>
+        <v>355.32</v>
       </c>
       <c r="G41">
         <v>293.6</v>
@@ -4649,28 +4649,28 @@
         <v>88.7</v>
       </c>
       <c r="M41">
-        <v>19.1579661</v>
+        <v>19.649196</v>
       </c>
       <c r="N41">
-        <v>69.54203390000001</v>
+        <v>69.050804</v>
       </c>
       <c r="O41">
-        <v>16.690088136</v>
+        <v>16.57219296</v>
       </c>
       <c r="P41">
-        <v>52.85194576400001</v>
+        <v>52.47861104</v>
       </c>
       <c r="Q41">
-        <v>85.251945764</v>
+        <v>84.87861104</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1035642315638635</v>
+        <v>0.1043714692806283</v>
       </c>
       <c r="T41">
-        <v>1.187693398860174</v>
+        <v>1.204291055949276</v>
       </c>
       <c r="U41">
         <v>0.0553</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>4.629927808463968</v>
+        <v>4.514179613252369</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.079434081568377</v>
+        <v>0.08008206188279723</v>
       </c>
       <c r="C42">
-        <v>540.7938188253695</v>
+        <v>524.3680978280449</v>
       </c>
       <c r="D42">
-        <v>602.5138188253695</v>
+        <v>594.9710978280449</v>
       </c>
       <c r="E42">
-        <v>-46.78000000000003</v>
+        <v>-37.89699999999999</v>
       </c>
       <c r="F42">
-        <v>355.32</v>
+        <v>364.203</v>
       </c>
       <c r="G42">
         <v>293.6</v>
@@ -4731,45 +4731,45 @@
         <v>88.7</v>
       </c>
       <c r="M42">
-        <v>19.649196</v>
+        <v>21.0509334</v>
       </c>
       <c r="N42">
-        <v>69.050804</v>
+        <v>67.6490666</v>
       </c>
       <c r="O42">
-        <v>16.57219296</v>
+        <v>16.235775984</v>
       </c>
       <c r="P42">
-        <v>52.47861104</v>
+        <v>51.413290616</v>
       </c>
       <c r="Q42">
-        <v>84.87861104</v>
+        <v>83.81329061599999</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1043714692806283</v>
+        <v>0.1052060709877919</v>
       </c>
       <c r="T42">
-        <v>1.204291055949276</v>
+        <v>1.221451345482077</v>
       </c>
       <c r="U42">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V42">
         <v>0.24</v>
       </c>
       <c r="W42">
-        <v>0.042028</v>
+        <v>0.043928</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y42">
-        <v>4.514179613252369</v>
+        <v>4.213589882907519</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.08008206188279723</v>
+        <v>0.07997004219721748</v>
       </c>
       <c r="C43">
-        <v>524.3680978280449</v>
+        <v>516.7755156378258</v>
       </c>
       <c r="D43">
-        <v>594.9710978280449</v>
+        <v>596.2615156378258</v>
       </c>
       <c r="E43">
-        <v>-37.89699999999999</v>
+        <v>-29.01400000000001</v>
       </c>
       <c r="F43">
-        <v>364.203</v>
+        <v>373.086</v>
       </c>
       <c r="G43">
         <v>293.6</v>
@@ -4813,28 +4813,28 @@
         <v>88.7</v>
       </c>
       <c r="M43">
-        <v>21.0509334</v>
+        <v>21.5643708</v>
       </c>
       <c r="N43">
-        <v>67.6490666</v>
+        <v>67.1356292</v>
       </c>
       <c r="O43">
-        <v>16.235775984</v>
+        <v>16.112551008</v>
       </c>
       <c r="P43">
-        <v>51.413290616</v>
+        <v>51.023078192</v>
       </c>
       <c r="Q43">
-        <v>83.81329061599999</v>
+        <v>83.42307819199999</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1052060709877919</v>
+        <v>0.1060694520641681</v>
       </c>
       <c r="T43">
-        <v>1.221451345482077</v>
+        <v>1.239203369136698</v>
       </c>
       <c r="U43">
         <v>0.0578</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>4.213589882907519</v>
+        <v>4.113266314266864</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.07997004219721748</v>
+        <v>0.07985802251163772</v>
       </c>
       <c r="C44">
-        <v>516.7755156378259</v>
+        <v>509.1885431235821</v>
       </c>
       <c r="D44">
-        <v>596.2615156378258</v>
+        <v>597.557543123582</v>
       </c>
       <c r="E44">
-        <v>-29.01400000000007</v>
+        <v>-20.13100000000003</v>
       </c>
       <c r="F44">
-        <v>373.086</v>
+        <v>381.969</v>
       </c>
       <c r="G44">
         <v>293.6</v>
@@ -4895,28 +4895,28 @@
         <v>88.7</v>
       </c>
       <c r="M44">
-        <v>21.5643708</v>
+        <v>22.0778082</v>
       </c>
       <c r="N44">
-        <v>67.13562920000001</v>
+        <v>66.6221918</v>
       </c>
       <c r="O44">
-        <v>16.112551008</v>
+        <v>15.989326032</v>
       </c>
       <c r="P44">
-        <v>51.02307819200001</v>
+        <v>50.63286576799999</v>
       </c>
       <c r="Q44">
-        <v>83.42307819200001</v>
+        <v>83.03286576799999</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1060694520641681</v>
+        <v>0.1069631272133995</v>
       </c>
       <c r="T44">
-        <v>1.239203369136698</v>
+        <v>1.257578270814288</v>
       </c>
       <c r="U44">
         <v>0.0578</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>4.113266314266865</v>
+        <v>4.017608958121123</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.07985802251163772</v>
+        <v>0.08091640282605794</v>
       </c>
       <c r="C45">
-        <v>509.1885431235821</v>
+        <v>488.2807930274698</v>
       </c>
       <c r="D45">
-        <v>597.557543123582</v>
+        <v>585.5327930274698</v>
       </c>
       <c r="E45">
-        <v>-20.13100000000003</v>
+        <v>-11.24800000000005</v>
       </c>
       <c r="F45">
-        <v>381.969</v>
+        <v>390.852</v>
       </c>
       <c r="G45">
         <v>293.6</v>
@@ -4977,45 +4977,45 @@
         <v>88.7</v>
       </c>
       <c r="M45">
-        <v>22.0778082</v>
+        <v>23.9592276</v>
       </c>
       <c r="N45">
-        <v>66.6221918</v>
+        <v>64.7407724</v>
       </c>
       <c r="O45">
-        <v>15.989326032</v>
+        <v>15.537785376</v>
       </c>
       <c r="P45">
-        <v>50.63286576799999</v>
+        <v>49.202987024</v>
       </c>
       <c r="Q45">
-        <v>83.03286576799999</v>
+        <v>81.60298702399999</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1069631272133995</v>
+        <v>0.1078887193322463</v>
       </c>
       <c r="T45">
-        <v>1.257578270814288</v>
+        <v>1.276609418980364</v>
       </c>
       <c r="U45">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V45">
         <v>0.24</v>
       </c>
       <c r="W45">
-        <v>0.043928</v>
+        <v>0.046588</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y45">
-        <v>4.017608958121123</v>
+        <v>3.702122684455821</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.08091640282605794</v>
+        <v>0.08083098314047819</v>
       </c>
       <c r="C46">
-        <v>488.2807930274698</v>
+        <v>480.3503033153372</v>
       </c>
       <c r="D46">
-        <v>585.5327930274698</v>
+        <v>586.4853033153372</v>
       </c>
       <c r="E46">
-        <v>-11.24800000000005</v>
+        <v>-2.365000000000009</v>
       </c>
       <c r="F46">
-        <v>390.852</v>
+        <v>399.735</v>
       </c>
       <c r="G46">
         <v>293.6</v>
@@ -5059,28 +5059,28 @@
         <v>88.7</v>
       </c>
       <c r="M46">
-        <v>23.9592276</v>
+        <v>24.5037555</v>
       </c>
       <c r="N46">
-        <v>64.7407724</v>
+        <v>64.19624450000001</v>
       </c>
       <c r="O46">
-        <v>15.537785376</v>
+        <v>15.40709868</v>
       </c>
       <c r="P46">
-        <v>49.202987024</v>
+        <v>48.78914582</v>
       </c>
       <c r="Q46">
-        <v>81.60298702399999</v>
+        <v>81.18914581999999</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1078887193322463</v>
+        <v>0.108847969346324</v>
       </c>
       <c r="T46">
-        <v>1.276609418980364</v>
+        <v>1.296332608897934</v>
       </c>
       <c r="U46">
         <v>0.0613</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>3.702122684455821</v>
+        <v>3.619853291467914</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.08083098314047819</v>
+        <v>0.08074556345489843</v>
       </c>
       <c r="C47">
-        <v>480.3503033153372</v>
+        <v>472.4229176280078</v>
       </c>
       <c r="D47">
-        <v>586.4853033153372</v>
+        <v>587.4409176280078</v>
       </c>
       <c r="E47">
-        <v>-2.365000000000009</v>
+        <v>6.517999999999972</v>
       </c>
       <c r="F47">
-        <v>399.735</v>
+        <v>408.618</v>
       </c>
       <c r="G47">
         <v>293.6</v>
@@ -5141,28 +5141,28 @@
         <v>88.7</v>
       </c>
       <c r="M47">
-        <v>24.5037555</v>
+        <v>25.0482834</v>
       </c>
       <c r="N47">
-        <v>64.19624450000001</v>
+        <v>63.6517166</v>
       </c>
       <c r="O47">
-        <v>15.40709868</v>
+        <v>15.276411984</v>
       </c>
       <c r="P47">
-        <v>48.78914582</v>
+        <v>48.375304616</v>
       </c>
       <c r="Q47">
-        <v>81.18914581999999</v>
+        <v>80.775304616</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.108847969346324</v>
+        <v>0.1098427471387008</v>
       </c>
       <c r="T47">
-        <v>1.296332608897934</v>
+        <v>1.316786287330969</v>
       </c>
       <c r="U47">
         <v>0.0613</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>3.619853291467914</v>
+        <v>3.541160828609916</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.08074556345489843</v>
+        <v>0.08166030376931867</v>
       </c>
       <c r="C48">
-        <v>472.4229176280078</v>
+        <v>453.4655685193658</v>
       </c>
       <c r="D48">
-        <v>587.4409176280078</v>
+        <v>577.3665685193657</v>
       </c>
       <c r="E48">
-        <v>6.517999999999972</v>
+        <v>15.40099999999995</v>
       </c>
       <c r="F48">
-        <v>408.618</v>
+        <v>417.501</v>
       </c>
       <c r="G48">
         <v>293.6</v>
@@ -5223,45 +5223,45 @@
         <v>88.7</v>
       </c>
       <c r="M48">
-        <v>25.0482834</v>
+        <v>26.7618141</v>
       </c>
       <c r="N48">
-        <v>63.6517166</v>
+        <v>61.93818590000001</v>
       </c>
       <c r="O48">
-        <v>15.276411984</v>
+        <v>14.865164616</v>
       </c>
       <c r="P48">
-        <v>48.375304616</v>
+        <v>47.07302128400001</v>
       </c>
       <c r="Q48">
-        <v>80.775304616</v>
+        <v>79.473021284</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1098427471387008</v>
+        <v>0.1108750637156956</v>
       </c>
       <c r="T48">
-        <v>1.316786287330969</v>
+        <v>1.338011802686005</v>
       </c>
       <c r="U48">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V48">
         <v>0.24</v>
       </c>
       <c r="W48">
-        <v>0.046588</v>
+        <v>0.048716</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y48">
-        <v>3.541160828609916</v>
+        <v>3.314424039736529</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.08166030376931867</v>
+        <v>0.0815961640837389</v>
       </c>
       <c r="C49">
-        <v>453.4655685193658</v>
+        <v>445.2776824502561</v>
       </c>
       <c r="D49">
-        <v>577.3665685193657</v>
+        <v>578.0616824502561</v>
       </c>
       <c r="E49">
-        <v>15.40099999999995</v>
+        <v>24.28399999999999</v>
       </c>
       <c r="F49">
-        <v>417.501</v>
+        <v>426.384</v>
       </c>
       <c r="G49">
         <v>293.6</v>
@@ -5305,28 +5305,28 @@
         <v>88.7</v>
       </c>
       <c r="M49">
-        <v>26.7618141</v>
+        <v>27.3312144</v>
       </c>
       <c r="N49">
-        <v>61.93818590000001</v>
+        <v>61.3687856</v>
       </c>
       <c r="O49">
-        <v>14.865164616</v>
+        <v>14.728508544</v>
       </c>
       <c r="P49">
-        <v>47.07302128400001</v>
+        <v>46.640277056</v>
       </c>
       <c r="Q49">
-        <v>79.473021284</v>
+        <v>79.04027705599998</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1108750637156956</v>
+        <v>0.111947084776421</v>
       </c>
       <c r="T49">
-        <v>1.338011802686005</v>
+        <v>1.360053684016235</v>
       </c>
       <c r="U49">
         <v>0.0641</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>3.314424039736529</v>
+        <v>3.245373538908684</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.0815961640837389</v>
+        <v>0.08153202439815914</v>
       </c>
       <c r="C50">
-        <v>445.2776824502561</v>
+        <v>437.0914721477308</v>
       </c>
       <c r="D50">
-        <v>578.0616824502561</v>
+        <v>578.7584721477308</v>
       </c>
       <c r="E50">
-        <v>24.28399999999993</v>
+        <v>33.16699999999997</v>
       </c>
       <c r="F50">
-        <v>426.384</v>
+        <v>435.267</v>
       </c>
       <c r="G50">
         <v>293.6</v>
@@ -5387,28 +5387,28 @@
         <v>88.7</v>
       </c>
       <c r="M50">
-        <v>27.3312144</v>
+        <v>27.9006147</v>
       </c>
       <c r="N50">
-        <v>61.3687856</v>
+        <v>60.7993853</v>
       </c>
       <c r="O50">
-        <v>14.728508544</v>
+        <v>14.591852472</v>
       </c>
       <c r="P50">
-        <v>46.640277056</v>
+        <v>46.207532828</v>
       </c>
       <c r="Q50">
-        <v>79.04027705599999</v>
+        <v>78.60753282799999</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.111947084776421</v>
+        <v>0.1130611458787434</v>
       </c>
       <c r="T50">
-        <v>1.360053684016235</v>
+        <v>1.382959952849611</v>
       </c>
       <c r="U50">
         <v>0.0641</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>3.245373538908685</v>
+        <v>3.179141425869731</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.08153202439815914</v>
+        <v>0.08146788471257939</v>
       </c>
       <c r="C51">
-        <v>437.0914721477308</v>
+        <v>428.9069436789594</v>
       </c>
       <c r="D51">
-        <v>578.7584721477308</v>
+        <v>579.4569436789593</v>
       </c>
       <c r="E51">
-        <v>33.16699999999997</v>
+        <v>42.04999999999995</v>
       </c>
       <c r="F51">
-        <v>435.267</v>
+        <v>444.15</v>
       </c>
       <c r="G51">
         <v>293.6</v>
@@ -5469,28 +5469,28 @@
         <v>88.7</v>
       </c>
       <c r="M51">
-        <v>27.9006147</v>
+        <v>28.470015</v>
       </c>
       <c r="N51">
-        <v>60.7993853</v>
+        <v>60.229985</v>
       </c>
       <c r="O51">
-        <v>14.591852472</v>
+        <v>14.4551964</v>
       </c>
       <c r="P51">
-        <v>46.207532828</v>
+        <v>45.7747886</v>
       </c>
       <c r="Q51">
-        <v>78.60753282799999</v>
+        <v>78.1747886</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1130611458787434</v>
+        <v>0.1142197694251588</v>
       </c>
       <c r="T51">
-        <v>1.382959952849611</v>
+        <v>1.406782472436323</v>
       </c>
       <c r="U51">
         <v>0.0641</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>3.179141425869731</v>
+        <v>3.115558597352337</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.08146788471257939</v>
+        <v>0.08140374502699962</v>
       </c>
       <c r="C52">
-        <v>428.9069436789594</v>
+        <v>420.7241031404357</v>
       </c>
       <c r="D52">
-        <v>579.4569436789593</v>
+        <v>580.1571031404357</v>
       </c>
       <c r="E52">
-        <v>42.04999999999995</v>
+        <v>50.93299999999994</v>
       </c>
       <c r="F52">
-        <v>444.15</v>
+        <v>453.033</v>
       </c>
       <c r="G52">
         <v>293.6</v>
@@ -5551,28 +5551,28 @@
         <v>88.7</v>
       </c>
       <c r="M52">
-        <v>28.470015</v>
+        <v>29.0394153</v>
       </c>
       <c r="N52">
-        <v>60.229985</v>
+        <v>59.6605847</v>
       </c>
       <c r="O52">
-        <v>14.4551964</v>
+        <v>14.318540328</v>
       </c>
       <c r="P52">
-        <v>45.7747886</v>
+        <v>45.342044372</v>
       </c>
       <c r="Q52">
-        <v>78.1747886</v>
+        <v>77.742044372</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1142197694251588</v>
+        <v>0.1154256837285706</v>
       </c>
       <c r="T52">
-        <v>1.406782472436323</v>
+        <v>1.431577339761267</v>
       </c>
       <c r="U52">
         <v>0.0641</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>3.115558597352337</v>
+        <v>3.054469213090527</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.08140374502699962</v>
+        <v>0.08442216534141986</v>
       </c>
       <c r="C53">
-        <v>420.7241031404357</v>
+        <v>380.6266552537493</v>
       </c>
       <c r="D53">
-        <v>580.1571031404357</v>
+        <v>548.9426552537493</v>
       </c>
       <c r="E53">
-        <v>50.93299999999994</v>
+        <v>59.81599999999997</v>
       </c>
       <c r="F53">
-        <v>453.033</v>
+        <v>461.916</v>
       </c>
       <c r="G53">
         <v>293.6</v>
@@ -5633,45 +5633,45 @@
         <v>88.7</v>
       </c>
       <c r="M53">
-        <v>29.0394153</v>
+        <v>33.2117604</v>
       </c>
       <c r="N53">
-        <v>59.6605847</v>
+        <v>55.4882396</v>
       </c>
       <c r="O53">
-        <v>14.318540328</v>
+        <v>13.317177504</v>
       </c>
       <c r="P53">
-        <v>45.342044372</v>
+        <v>42.171062096</v>
       </c>
       <c r="Q53">
-        <v>77.742044372</v>
+        <v>74.57106209599999</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1154256837285706</v>
+        <v>0.1166818444612914</v>
       </c>
       <c r="T53">
-        <v>1.431577339761267</v>
+        <v>1.457405326558084</v>
       </c>
       <c r="U53">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V53">
         <v>0.24</v>
       </c>
       <c r="W53">
-        <v>0.048716</v>
+        <v>0.05464400000000001</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y53">
-        <v>3.054469213090527</v>
+        <v>2.670740693408109</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.08442216534141986</v>
+        <v>0.0844173056558401</v>
       </c>
       <c r="C54">
-        <v>380.6266552537493</v>
+        <v>371.7912110109197</v>
       </c>
       <c r="D54">
-        <v>548.9426552537493</v>
+        <v>548.9902110109197</v>
       </c>
       <c r="E54">
-        <v>59.81599999999997</v>
+        <v>68.69899999999996</v>
       </c>
       <c r="F54">
-        <v>461.916</v>
+        <v>470.799</v>
       </c>
       <c r="G54">
         <v>293.6</v>
@@ -5715,28 +5715,28 @@
         <v>88.7</v>
       </c>
       <c r="M54">
-        <v>33.2117604</v>
+        <v>33.8504481</v>
       </c>
       <c r="N54">
-        <v>55.4882396</v>
+        <v>54.8495519</v>
       </c>
       <c r="O54">
-        <v>13.317177504</v>
+        <v>13.163892456</v>
       </c>
       <c r="P54">
-        <v>42.171062096</v>
+        <v>41.685659444</v>
       </c>
       <c r="Q54">
-        <v>74.57106209599999</v>
+        <v>74.08565944399999</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1166818444612914</v>
+        <v>0.117991458842213</v>
       </c>
       <c r="T54">
-        <v>1.457405326558084</v>
+        <v>1.484332376622851</v>
       </c>
       <c r="U54">
         <v>0.07190000000000001</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>2.670740693408109</v>
+        <v>2.620349359570221</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.0844173056558401</v>
+        <v>0.08441244597026033</v>
       </c>
       <c r="C55">
-        <v>371.7912110109197</v>
+        <v>362.9557750084628</v>
       </c>
       <c r="D55">
-        <v>548.9902110109197</v>
+        <v>549.0377750084627</v>
       </c>
       <c r="E55">
-        <v>68.69899999999996</v>
+        <v>77.58199999999999</v>
       </c>
       <c r="F55">
-        <v>470.799</v>
+        <v>479.682</v>
       </c>
       <c r="G55">
         <v>293.6</v>
@@ -5797,28 +5797,28 @@
         <v>88.7</v>
       </c>
       <c r="M55">
-        <v>33.8504481</v>
+        <v>34.48913580000001</v>
       </c>
       <c r="N55">
-        <v>54.8495519</v>
+        <v>54.2108642</v>
       </c>
       <c r="O55">
-        <v>13.163892456</v>
+        <v>13.010607408</v>
       </c>
       <c r="P55">
-        <v>41.685659444</v>
+        <v>41.200256792</v>
       </c>
       <c r="Q55">
-        <v>74.08565944399999</v>
+        <v>73.60025679199998</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.117991458842213</v>
+        <v>0.1193580129788268</v>
       </c>
       <c r="T55">
-        <v>1.484332376622851</v>
+        <v>1.512430167994782</v>
       </c>
       <c r="U55">
         <v>0.07190000000000001</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>2.620349359570221</v>
+        <v>2.571824371430031</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.08441244597026033</v>
+        <v>0.08440758628468056</v>
       </c>
       <c r="C56">
-        <v>362.9557750084628</v>
+        <v>354.1203472485202</v>
       </c>
       <c r="D56">
-        <v>549.0377750084627</v>
+        <v>549.0853472485202</v>
       </c>
       <c r="E56">
-        <v>77.58199999999999</v>
+        <v>86.46499999999997</v>
       </c>
       <c r="F56">
-        <v>479.682</v>
+        <v>488.565</v>
       </c>
       <c r="G56">
         <v>293.6</v>
@@ -5879,28 +5879,28 @@
         <v>88.7</v>
       </c>
       <c r="M56">
-        <v>34.48913580000001</v>
+        <v>35.12782350000001</v>
       </c>
       <c r="N56">
-        <v>54.2108642</v>
+        <v>53.5721765</v>
       </c>
       <c r="O56">
-        <v>13.010607408</v>
+        <v>12.85732236</v>
       </c>
       <c r="P56">
-        <v>41.200256792</v>
+        <v>40.71485414</v>
       </c>
       <c r="Q56">
-        <v>73.60025679199998</v>
+        <v>73.11485413999999</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1193580129788268</v>
+        <v>0.1207853028548457</v>
       </c>
       <c r="T56">
-        <v>1.512430167994782</v>
+        <v>1.541776750094354</v>
       </c>
       <c r="U56">
         <v>0.07190000000000001</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>2.571824371430031</v>
+        <v>2.525063928313122</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.08440758628468056</v>
+        <v>0.0860625665991008</v>
       </c>
       <c r="C57">
-        <v>354.1203472485202</v>
+        <v>329.4994656909786</v>
       </c>
       <c r="D57">
-        <v>549.0853472485202</v>
+        <v>533.3474656909787</v>
       </c>
       <c r="E57">
-        <v>86.46499999999997</v>
+        <v>95.34800000000001</v>
       </c>
       <c r="F57">
-        <v>488.565</v>
+        <v>497.448</v>
       </c>
       <c r="G57">
         <v>293.6</v>
@@ -5961,45 +5961,45 @@
         <v>88.7</v>
       </c>
       <c r="M57">
-        <v>35.12782350000001</v>
+        <v>37.70655840000001</v>
       </c>
       <c r="N57">
-        <v>53.5721765</v>
+        <v>50.9934416</v>
       </c>
       <c r="O57">
-        <v>12.85732236</v>
+        <v>12.238425984</v>
       </c>
       <c r="P57">
-        <v>40.71485414</v>
+        <v>38.75501561599999</v>
       </c>
       <c r="Q57">
-        <v>73.11485413999999</v>
+        <v>71.15501561599999</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1207853028548457</v>
+        <v>0.1222774695434109</v>
       </c>
       <c r="T57">
-        <v>1.541776750094354</v>
+        <v>1.572457267743906</v>
       </c>
       <c r="U57">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V57">
         <v>0.24</v>
       </c>
       <c r="W57">
-        <v>0.05464400000000001</v>
+        <v>0.05760800000000001</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y57">
-        <v>2.525063928313122</v>
+        <v>2.352375919834678</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.0860625665991008</v>
+        <v>0.08608734691352105</v>
       </c>
       <c r="C58">
-        <v>329.4994656909786</v>
+        <v>320.3876718697472</v>
       </c>
       <c r="D58">
-        <v>533.3474656909787</v>
+        <v>533.1186718697472</v>
       </c>
       <c r="E58">
-        <v>95.34800000000001</v>
+        <v>104.231</v>
       </c>
       <c r="F58">
-        <v>497.448</v>
+        <v>506.331</v>
       </c>
       <c r="G58">
         <v>293.6</v>
@@ -6043,28 +6043,28 @@
         <v>88.7</v>
       </c>
       <c r="M58">
-        <v>37.70655840000001</v>
+        <v>38.37988980000001</v>
       </c>
       <c r="N58">
-        <v>50.9934416</v>
+        <v>50.32011019999999</v>
       </c>
       <c r="O58">
-        <v>12.238425984</v>
+        <v>12.076826448</v>
       </c>
       <c r="P58">
-        <v>38.75501561599999</v>
+        <v>38.243283752</v>
       </c>
       <c r="Q58">
-        <v>71.15501561599999</v>
+        <v>70.64328375199999</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1222774695434109</v>
+        <v>0.1238390393337699</v>
       </c>
       <c r="T58">
-        <v>1.572457267743906</v>
+        <v>1.604564786214368</v>
       </c>
       <c r="U58">
         <v>0.07580000000000001</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>2.352375919834678</v>
+        <v>2.311106166855122</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.08608734691352105</v>
+        <v>0.08611212722794129</v>
       </c>
       <c r="C59">
-        <v>320.3876718697472</v>
+        <v>311.276074258942</v>
       </c>
       <c r="D59">
-        <v>533.1186718697472</v>
+        <v>532.890074258942</v>
       </c>
       <c r="E59">
-        <v>104.231</v>
+        <v>113.114</v>
       </c>
       <c r="F59">
-        <v>506.331</v>
+        <v>515.2140000000001</v>
       </c>
       <c r="G59">
         <v>293.6</v>
@@ -6125,28 +6125,28 @@
         <v>88.7</v>
       </c>
       <c r="M59">
-        <v>38.37988980000001</v>
+        <v>39.05322120000001</v>
       </c>
       <c r="N59">
-        <v>50.32011019999999</v>
+        <v>49.64677879999999</v>
       </c>
       <c r="O59">
-        <v>12.076826448</v>
+        <v>11.915226912</v>
       </c>
       <c r="P59">
-        <v>38.243283752</v>
+        <v>37.731551888</v>
       </c>
       <c r="Q59">
-        <v>70.64328375199999</v>
+        <v>70.13155188799999</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1238390393337699</v>
+        <v>0.1254749695903364</v>
       </c>
       <c r="T59">
-        <v>1.604564786214368</v>
+        <v>1.638201234135804</v>
       </c>
       <c r="U59">
         <v>0.07580000000000001</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>2.311106166855122</v>
+        <v>2.271259508805895</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.08611212722794129</v>
+        <v>0.08613690754236153</v>
       </c>
       <c r="C60">
-        <v>311.2760742589421</v>
+        <v>302.1646726062701</v>
       </c>
       <c r="D60">
-        <v>532.890074258942</v>
+        <v>532.66167260627</v>
       </c>
       <c r="E60">
-        <v>113.1139999999999</v>
+        <v>121.997</v>
       </c>
       <c r="F60">
-        <v>515.2139999999999</v>
+        <v>524.097</v>
       </c>
       <c r="G60">
         <v>293.6</v>
@@ -6207,28 +6207,28 @@
         <v>88.7</v>
       </c>
       <c r="M60">
-        <v>39.0532212</v>
+        <v>39.72655260000001</v>
       </c>
       <c r="N60">
-        <v>49.64677880000001</v>
+        <v>48.9734474</v>
       </c>
       <c r="O60">
-        <v>11.915226912</v>
+        <v>11.753627376</v>
       </c>
       <c r="P60">
-        <v>37.73155188800001</v>
+        <v>37.219820024</v>
       </c>
       <c r="Q60">
-        <v>70.13155188799999</v>
+        <v>69.61982002399999</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1254749695903364</v>
+        <v>0.127190701322833</v>
       </c>
       <c r="T60">
-        <v>1.638201234135804</v>
+        <v>1.673478484394872</v>
       </c>
       <c r="U60">
         <v>0.07580000000000001</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>2.271259508805896</v>
+        <v>2.23276358492783</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.08613690754236153</v>
+        <v>0.08616168785678177</v>
       </c>
       <c r="C61">
-        <v>302.1646726062701</v>
+        <v>293.053466659871</v>
       </c>
       <c r="D61">
-        <v>532.66167260627</v>
+        <v>532.4334666598709</v>
       </c>
       <c r="E61">
-        <v>121.997</v>
+        <v>130.8799999999999</v>
       </c>
       <c r="F61">
-        <v>524.097</v>
+        <v>532.9799999999999</v>
       </c>
       <c r="G61">
         <v>293.6</v>
@@ -6289,28 +6289,28 @@
         <v>88.7</v>
       </c>
       <c r="M61">
-        <v>39.72655260000001</v>
+        <v>40.39988399999999</v>
       </c>
       <c r="N61">
-        <v>48.9734474</v>
+        <v>48.30011600000001</v>
       </c>
       <c r="O61">
-        <v>11.753627376</v>
+        <v>11.59202784</v>
       </c>
       <c r="P61">
-        <v>37.219820024</v>
+        <v>36.70808816000001</v>
       </c>
       <c r="Q61">
-        <v>69.61982002399999</v>
+        <v>69.10808815999999</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.127190701322833</v>
+        <v>0.1289922196419544</v>
       </c>
       <c r="T61">
-        <v>1.673478484394872</v>
+        <v>1.710519597166892</v>
       </c>
       <c r="U61">
         <v>0.07580000000000001</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>2.23276358492783</v>
+        <v>2.195550858512366</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.08616168785678177</v>
+        <v>0.08618646817120201</v>
       </c>
       <c r="C62">
-        <v>293.053466659871</v>
+        <v>283.9424561683156</v>
       </c>
       <c r="D62">
-        <v>532.4334666598709</v>
+        <v>532.2054561683155</v>
       </c>
       <c r="E62">
-        <v>130.8799999999999</v>
+        <v>139.7629999999999</v>
       </c>
       <c r="F62">
-        <v>532.9799999999999</v>
+        <v>541.8629999999999</v>
       </c>
       <c r="G62">
         <v>293.6</v>
@@ -6371,28 +6371,28 @@
         <v>88.7</v>
       </c>
       <c r="M62">
-        <v>40.39988399999999</v>
+        <v>41.0732154</v>
       </c>
       <c r="N62">
-        <v>48.30011600000001</v>
+        <v>47.6267846</v>
       </c>
       <c r="O62">
-        <v>11.59202784</v>
+        <v>11.430428304</v>
       </c>
       <c r="P62">
-        <v>36.70808816000001</v>
+        <v>36.196356296</v>
       </c>
       <c r="Q62">
-        <v>69.10808815999999</v>
+        <v>68.596356296</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1289922196419544</v>
+        <v>0.1308861235159026</v>
       </c>
       <c r="T62">
-        <v>1.710519597166892</v>
+        <v>1.749460254183632</v>
       </c>
       <c r="U62">
         <v>0.07580000000000001</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>2.195550858512366</v>
+        <v>2.159558221487573</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.08618646817120201</v>
+        <v>0.08621124848562225</v>
       </c>
       <c r="C63">
-        <v>283.9424561683156</v>
+        <v>274.8316408806054</v>
       </c>
       <c r="D63">
-        <v>532.2054561683155</v>
+        <v>531.9776408806053</v>
       </c>
       <c r="E63">
-        <v>139.7629999999999</v>
+        <v>148.646</v>
       </c>
       <c r="F63">
-        <v>541.8629999999999</v>
+        <v>550.746</v>
       </c>
       <c r="G63">
         <v>293.6</v>
@@ -6453,28 +6453,28 @@
         <v>88.7</v>
       </c>
       <c r="M63">
-        <v>41.0732154</v>
+        <v>41.7465468</v>
       </c>
       <c r="N63">
-        <v>47.6267846</v>
+        <v>46.9534532</v>
       </c>
       <c r="O63">
-        <v>11.430428304</v>
+        <v>11.268828768</v>
       </c>
       <c r="P63">
-        <v>36.196356296</v>
+        <v>35.684624432</v>
       </c>
       <c r="Q63">
-        <v>68.596356296</v>
+        <v>68.084624432</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1308861235159026</v>
+        <v>0.1328797065411112</v>
       </c>
       <c r="T63">
-        <v>1.749460254183632</v>
+        <v>1.790450419464411</v>
       </c>
       <c r="U63">
         <v>0.07580000000000001</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>2.159558221487573</v>
+        <v>2.124726637270031</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.08621124848562225</v>
+        <v>0.08623602880004247</v>
       </c>
       <c r="C64">
-        <v>274.8316408806054</v>
+        <v>265.7210205461716</v>
       </c>
       <c r="D64">
-        <v>531.9776408806053</v>
+        <v>531.7500205461716</v>
       </c>
       <c r="E64">
-        <v>148.646</v>
+        <v>157.529</v>
       </c>
       <c r="F64">
-        <v>550.746</v>
+        <v>559.629</v>
       </c>
       <c r="G64">
         <v>293.6</v>
@@ -6535,28 +6535,28 @@
         <v>88.7</v>
       </c>
       <c r="M64">
-        <v>41.7465468</v>
+        <v>42.41987820000001</v>
       </c>
       <c r="N64">
-        <v>46.9534532</v>
+        <v>46.2801218</v>
       </c>
       <c r="O64">
-        <v>11.268828768</v>
+        <v>11.107229232</v>
       </c>
       <c r="P64">
-        <v>35.684624432</v>
+        <v>35.17289256799999</v>
       </c>
       <c r="Q64">
-        <v>68.084624432</v>
+        <v>67.57289256799999</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1328797065411112</v>
+        <v>0.1349810508109256</v>
       </c>
       <c r="T64">
-        <v>1.790450419464411</v>
+        <v>1.833656269354961</v>
       </c>
       <c r="U64">
         <v>0.07580000000000001</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>2.124726637270031</v>
+        <v>2.091000817630825</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.08623602880004247</v>
+        <v>0.08626080911446271</v>
       </c>
       <c r="C65">
-        <v>265.7210205461716</v>
+        <v>256.6105949148736</v>
       </c>
       <c r="D65">
-        <v>531.7500205461716</v>
+        <v>531.5225949148735</v>
       </c>
       <c r="E65">
-        <v>157.529</v>
+        <v>166.4119999999999</v>
       </c>
       <c r="F65">
-        <v>559.629</v>
+        <v>568.5119999999999</v>
       </c>
       <c r="G65">
         <v>293.6</v>
@@ -6617,28 +6617,28 @@
         <v>88.7</v>
       </c>
       <c r="M65">
-        <v>42.41987820000001</v>
+        <v>43.0932096</v>
       </c>
       <c r="N65">
-        <v>46.2801218</v>
+        <v>45.6067904</v>
       </c>
       <c r="O65">
-        <v>11.107229232</v>
+        <v>10.945629696</v>
       </c>
       <c r="P65">
-        <v>35.17289256799999</v>
+        <v>34.661160704</v>
       </c>
       <c r="Q65">
-        <v>67.57289256799999</v>
+        <v>67.061160704</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1349810508109256</v>
+        <v>0.1371991364290631</v>
       </c>
       <c r="T65">
-        <v>1.833656269354961</v>
+        <v>1.879262444239431</v>
       </c>
       <c r="U65">
         <v>0.07580000000000001</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>2.091000817630825</v>
+        <v>2.058328929855343</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.08626080911446271</v>
+        <v>0.08628558942888295</v>
       </c>
       <c r="C66">
-        <v>256.6105949148736</v>
+        <v>247.5003637369988</v>
       </c>
       <c r="D66">
-        <v>531.5225949148735</v>
+        <v>531.2953637369988</v>
       </c>
       <c r="E66">
-        <v>166.4119999999999</v>
+        <v>175.295</v>
       </c>
       <c r="F66">
-        <v>568.5119999999999</v>
+        <v>577.395</v>
       </c>
       <c r="G66">
         <v>293.6</v>
@@ -6699,28 +6699,28 @@
         <v>88.7</v>
       </c>
       <c r="M66">
-        <v>43.0932096</v>
+        <v>43.766541</v>
       </c>
       <c r="N66">
-        <v>45.6067904</v>
+        <v>44.933459</v>
       </c>
       <c r="O66">
-        <v>10.945629696</v>
+        <v>10.78403016</v>
       </c>
       <c r="P66">
-        <v>34.661160704</v>
+        <v>34.14942884</v>
       </c>
       <c r="Q66">
-        <v>67.061160704</v>
+        <v>66.54942883999999</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1371991364290631</v>
+        <v>0.1395439697968084</v>
       </c>
       <c r="T66">
-        <v>1.879262444239431</v>
+        <v>1.927474686260157</v>
       </c>
       <c r="U66">
         <v>0.07580000000000001</v>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>2.058328929855343</v>
+        <v>2.026662330934491</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.08628558942888295</v>
+        <v>0.09343308974330319</v>
       </c>
       <c r="C67">
-        <v>247.5003637369988</v>
+        <v>180.2956226646759</v>
       </c>
       <c r="D67">
-        <v>531.2953637369988</v>
+        <v>472.9736226646759</v>
       </c>
       <c r="E67">
-        <v>175.295</v>
+        <v>184.178</v>
       </c>
       <c r="F67">
-        <v>577.395</v>
+        <v>586.278</v>
       </c>
       <c r="G67">
         <v>293.6</v>
@@ -6781,45 +6781,45 @@
         <v>88.7</v>
       </c>
       <c r="M67">
-        <v>43.766541</v>
+        <v>52.76502</v>
       </c>
       <c r="N67">
-        <v>44.933459</v>
+        <v>35.93498</v>
       </c>
       <c r="O67">
-        <v>10.78403016</v>
+        <v>8.6243952</v>
       </c>
       <c r="P67">
-        <v>34.14942884</v>
+        <v>27.3105848</v>
       </c>
       <c r="Q67">
-        <v>66.54942883999999</v>
+        <v>59.71058479999999</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1395439697968084</v>
+        <v>0.142026734539127</v>
       </c>
       <c r="T67">
-        <v>1.927474686260157</v>
+        <v>1.978522942517395</v>
       </c>
       <c r="U67">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V67">
         <v>0.24</v>
       </c>
       <c r="W67">
-        <v>0.05760800000000001</v>
+        <v>0.0684</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y67">
-        <v>2.026662330934491</v>
+        <v>1.681037930052903</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.09343308974330319</v>
+        <v>0.09356579005772345</v>
       </c>
       <c r="C68">
-        <v>180.2956226646759</v>
+        <v>170.4506451156815</v>
       </c>
       <c r="D68">
-        <v>472.9736226646759</v>
+        <v>472.0116451156815</v>
       </c>
       <c r="E68">
-        <v>184.178</v>
+        <v>193.061</v>
       </c>
       <c r="F68">
-        <v>586.278</v>
+        <v>595.1610000000001</v>
       </c>
       <c r="G68">
         <v>293.6</v>
@@ -6863,28 +6863,28 @@
         <v>88.7</v>
       </c>
       <c r="M68">
-        <v>52.76502</v>
+        <v>53.56449000000001</v>
       </c>
       <c r="N68">
-        <v>35.93498</v>
+        <v>35.13551</v>
       </c>
       <c r="O68">
-        <v>8.6243952</v>
+        <v>8.432522399999998</v>
       </c>
       <c r="P68">
-        <v>27.3105848</v>
+        <v>26.7029876</v>
       </c>
       <c r="Q68">
-        <v>59.71058479999999</v>
+        <v>59.10298759999999</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.142026734539127</v>
+        <v>0.1446599698718892</v>
       </c>
       <c r="T68">
-        <v>1.978522942517395</v>
+        <v>2.032665032487194</v>
       </c>
       <c r="U68">
         <v>0.09</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>1.681037930052903</v>
+        <v>1.655947811693904</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.09356579005772345</v>
+        <v>0.09369849037214367</v>
       </c>
       <c r="C69">
-        <v>170.4506451156815</v>
+        <v>160.6095727420081</v>
       </c>
       <c r="D69">
-        <v>472.0116451156815</v>
+        <v>471.0535727420081</v>
       </c>
       <c r="E69">
-        <v>193.061</v>
+        <v>201.944</v>
       </c>
       <c r="F69">
-        <v>595.1610000000001</v>
+        <v>604.044</v>
       </c>
       <c r="G69">
         <v>293.6</v>
@@ -6945,28 +6945,28 @@
         <v>88.7</v>
       </c>
       <c r="M69">
-        <v>53.56449000000001</v>
+        <v>54.36396</v>
       </c>
       <c r="N69">
-        <v>35.13551</v>
+        <v>34.33604</v>
       </c>
       <c r="O69">
-        <v>8.432522399999998</v>
+        <v>8.240649600000001</v>
       </c>
       <c r="P69">
-        <v>26.7029876</v>
+        <v>26.0953904</v>
       </c>
       <c r="Q69">
-        <v>59.10298759999999</v>
+        <v>58.49539039999999</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1446599698718892</v>
+        <v>0.147457782412949</v>
       </c>
       <c r="T69">
-        <v>2.032665032487194</v>
+        <v>2.090191003080105</v>
       </c>
       <c r="U69">
         <v>0.09</v>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>1.655947811693904</v>
+        <v>1.631595637992523</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.09369849037214367</v>
+        <v>0.09383119068656393</v>
       </c>
       <c r="C70">
-        <v>160.6095727420081</v>
+        <v>150.7723818120686</v>
       </c>
       <c r="D70">
-        <v>471.0535727420081</v>
+        <v>470.0993818120686</v>
       </c>
       <c r="E70">
-        <v>201.944</v>
+        <v>210.827</v>
       </c>
       <c r="F70">
-        <v>604.044</v>
+        <v>612.927</v>
       </c>
       <c r="G70">
         <v>293.6</v>
@@ -7027,28 +7027,28 @@
         <v>88.7</v>
       </c>
       <c r="M70">
-        <v>54.36396</v>
+        <v>55.16343</v>
       </c>
       <c r="N70">
-        <v>34.33604</v>
+        <v>33.53657</v>
       </c>
       <c r="O70">
-        <v>8.240649600000001</v>
+        <v>8.048776800000001</v>
       </c>
       <c r="P70">
-        <v>26.0953904</v>
+        <v>25.48779320000001</v>
       </c>
       <c r="Q70">
-        <v>58.49539039999999</v>
+        <v>57.8877932</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.147457782412949</v>
+        <v>0.1504360989889159</v>
       </c>
       <c r="T70">
-        <v>2.090191003080105</v>
+        <v>2.151428326614494</v>
       </c>
       <c r="U70">
         <v>0.09</v>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>1.631595637992523</v>
+        <v>1.607949324398429</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.09383119068656393</v>
+        <v>0.09396389100098414</v>
       </c>
       <c r="C71">
-        <v>150.7723818120686</v>
+        <v>140.939048786176</v>
       </c>
       <c r="D71">
-        <v>470.0993818120686</v>
+        <v>469.1490487861761</v>
       </c>
       <c r="E71">
-        <v>210.827</v>
+        <v>219.71</v>
       </c>
       <c r="F71">
-        <v>612.927</v>
+        <v>621.8100000000001</v>
       </c>
       <c r="G71">
         <v>293.6</v>
@@ -7109,28 +7109,28 @@
         <v>88.7</v>
       </c>
       <c r="M71">
-        <v>55.16343</v>
+        <v>55.9629</v>
       </c>
       <c r="N71">
-        <v>33.53657</v>
+        <v>32.7371</v>
       </c>
       <c r="O71">
-        <v>8.048776800000001</v>
+        <v>7.856903999999999</v>
       </c>
       <c r="P71">
-        <v>25.48779320000001</v>
+        <v>24.880196</v>
       </c>
       <c r="Q71">
-        <v>57.8877932</v>
+        <v>57.28019599999999</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1504360989889159</v>
+        <v>0.1536129700032805</v>
       </c>
       <c r="T71">
-        <v>2.151428326614494</v>
+        <v>2.216748138384509</v>
       </c>
       <c r="U71">
         <v>0.09</v>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>1.607949324398429</v>
+        <v>1.584978619764165</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.09396389100098414</v>
+        <v>0.09409659131540439</v>
       </c>
       <c r="C72">
-        <v>140.939048786176</v>
+        <v>131.1095503146059</v>
       </c>
       <c r="D72">
-        <v>469.1490487861761</v>
+        <v>468.202550314606</v>
       </c>
       <c r="E72">
-        <v>219.71</v>
+        <v>228.593</v>
       </c>
       <c r="F72">
-        <v>621.8100000000001</v>
+        <v>630.693</v>
       </c>
       <c r="G72">
         <v>293.6</v>
@@ -7191,28 +7191,28 @@
         <v>88.7</v>
       </c>
       <c r="M72">
-        <v>55.9629</v>
+        <v>56.76237</v>
       </c>
       <c r="N72">
-        <v>32.7371</v>
+        <v>31.93763000000001</v>
       </c>
       <c r="O72">
-        <v>7.856903999999999</v>
+        <v>7.665031200000001</v>
       </c>
       <c r="P72">
-        <v>24.880196</v>
+        <v>24.2725988</v>
       </c>
       <c r="Q72">
-        <v>57.28019599999999</v>
+        <v>56.6725988</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1536129700032805</v>
+        <v>0.15700893557036</v>
       </c>
       <c r="T72">
-        <v>2.216748138384509</v>
+        <v>2.286572764759353</v>
       </c>
       <c r="U72">
         <v>0.09</v>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>1.584978619764165</v>
+        <v>1.562654977232276</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.09409659131540438</v>
+        <v>0.09422929162982463</v>
       </c>
       <c r="C73">
-        <v>131.1095503146061</v>
+        <v>121.2838632356855</v>
       </c>
       <c r="D73">
-        <v>468.202550314606</v>
+        <v>467.2598632356854</v>
       </c>
       <c r="E73">
-        <v>228.593</v>
+        <v>237.4759999999999</v>
       </c>
       <c r="F73">
-        <v>630.693</v>
+        <v>639.5759999999999</v>
       </c>
       <c r="G73">
         <v>293.6</v>
@@ -7273,28 +7273,28 @@
         <v>88.7</v>
       </c>
       <c r="M73">
-        <v>56.76237</v>
+        <v>57.56183999999999</v>
       </c>
       <c r="N73">
-        <v>31.93763000000001</v>
+        <v>31.13816000000001</v>
       </c>
       <c r="O73">
-        <v>7.665031200000001</v>
+        <v>7.473158400000003</v>
       </c>
       <c r="P73">
-        <v>24.2725988</v>
+        <v>23.66500160000001</v>
       </c>
       <c r="Q73">
-        <v>56.6725988</v>
+        <v>56.0650016</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1570089355703599</v>
+        <v>0.1606474701065165</v>
       </c>
       <c r="T73">
-        <v>2.286572764759352</v>
+        <v>2.361384864446685</v>
       </c>
       <c r="U73">
         <v>0.09</v>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>1.562654977232276</v>
+        <v>1.540951435881828</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.09422929162982463</v>
+        <v>0.09436199194424486</v>
       </c>
       <c r="C74">
-        <v>121.2838632356855</v>
+        <v>111.4619645739029</v>
       </c>
       <c r="D74">
-        <v>467.2598632356854</v>
+        <v>466.3209645739029</v>
       </c>
       <c r="E74">
-        <v>237.4759999999999</v>
+        <v>246.3589999999999</v>
       </c>
       <c r="F74">
-        <v>639.5759999999999</v>
+        <v>648.4589999999999</v>
       </c>
       <c r="G74">
         <v>293.6</v>
@@ -7355,28 +7355,28 @@
         <v>88.7</v>
       </c>
       <c r="M74">
-        <v>57.56183999999999</v>
+        <v>58.36131</v>
       </c>
       <c r="N74">
-        <v>31.13816000000001</v>
+        <v>30.33869000000001</v>
       </c>
       <c r="O74">
-        <v>7.473158400000003</v>
+        <v>7.281285600000001</v>
       </c>
       <c r="P74">
-        <v>23.66500160000001</v>
+        <v>23.05740440000001</v>
       </c>
       <c r="Q74">
-        <v>56.0650016</v>
+        <v>55.4574044</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1606474701065165</v>
+        <v>0.1645555257194254</v>
       </c>
       <c r="T74">
-        <v>2.361384864446685</v>
+        <v>2.441738601147893</v>
       </c>
       <c r="U74">
         <v>0.09</v>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>1.540951435881828</v>
+        <v>1.519842512102624</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.09436199194424486</v>
+        <v>0.1291037290229251</v>
       </c>
       <c r="C75">
-        <v>111.4619645739029</v>
+        <v>-58.17125939900632</v>
       </c>
       <c r="D75">
-        <v>466.3209645739029</v>
+        <v>305.5707406009937</v>
       </c>
       <c r="E75">
-        <v>246.3589999999999</v>
+        <v>255.242</v>
       </c>
       <c r="F75">
-        <v>648.4589999999999</v>
+        <v>657.342</v>
       </c>
       <c r="G75">
         <v>293.6</v>
@@ -7437,45 +7437,45 @@
         <v>88.7</v>
       </c>
       <c r="M75">
-        <v>58.36131</v>
+        <v>96.49780560000001</v>
       </c>
       <c r="N75">
-        <v>30.33869000000001</v>
+        <v>-7.797805600000004</v>
       </c>
       <c r="O75">
-        <v>7.281285600000001</v>
+        <v>-1.871473344000001</v>
       </c>
       <c r="P75">
-        <v>23.05740440000001</v>
+        <v>-5.926332256000003</v>
       </c>
       <c r="Q75">
-        <v>55.4574044</v>
+        <v>26.47366774399999</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1645555257194254</v>
+        <v>0.1709100221298434</v>
       </c>
       <c r="T75">
-        <v>2.441738601147893</v>
+        <v>2.572393735569444</v>
       </c>
       <c r="U75">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V75">
-        <v>0.24</v>
+        <v>0.2206060528282106</v>
       </c>
       <c r="W75">
-        <v>0.0684</v>
+        <v>0.1144150314448187</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y75">
-        <v>1.519842512102624</v>
+        <v>0.9191918867842109</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1291037290229251</v>
+        <v>0.1301137290229251</v>
       </c>
       <c r="C76">
-        <v>-58.17125939900632</v>
+        <v>-70.08617844688501</v>
       </c>
       <c r="D76">
-        <v>305.5707406009937</v>
+        <v>302.5388215531148</v>
       </c>
       <c r="E76">
-        <v>255.242</v>
+        <v>264.1249999999999</v>
       </c>
       <c r="F76">
-        <v>657.342</v>
+        <v>666.2249999999999</v>
       </c>
       <c r="G76">
         <v>293.6</v>
@@ -7519,37 +7519,37 @@
         <v>88.7</v>
       </c>
       <c r="M76">
-        <v>96.49780560000001</v>
+        <v>97.80183</v>
       </c>
       <c r="N76">
-        <v>-7.797805600000004</v>
+        <v>-9.101829999999993</v>
       </c>
       <c r="O76">
-        <v>-1.871473344000001</v>
+        <v>-2.184439199999998</v>
       </c>
       <c r="P76">
-        <v>-5.926332256000003</v>
+        <v>-6.917390799999994</v>
       </c>
       <c r="Q76">
-        <v>26.47366774399999</v>
+        <v>25.4826092</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1709100221298434</v>
+        <v>0.1759144230150372</v>
       </c>
       <c r="T76">
-        <v>2.572393735569444</v>
+        <v>2.675289484992221</v>
       </c>
       <c r="U76">
         <v>0.1468</v>
       </c>
       <c r="V76">
-        <v>0.2206060528282106</v>
+        <v>0.2176646387905012</v>
       </c>
       <c r="W76">
-        <v>0.1144150314448187</v>
+        <v>0.1148468310255544</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.9191918867842109</v>
+        <v>0.9069359949604215</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1301137290229251</v>
+        <v>0.1311237290229251</v>
       </c>
       <c r="C77">
-        <v>-70.08617844688501</v>
+        <v>-81.94152229133999</v>
       </c>
       <c r="D77">
-        <v>302.5388215531148</v>
+        <v>299.5664777086599</v>
       </c>
       <c r="E77">
-        <v>264.1249999999999</v>
+        <v>273.0079999999999</v>
       </c>
       <c r="F77">
-        <v>666.2249999999999</v>
+        <v>675.1079999999999</v>
       </c>
       <c r="G77">
         <v>293.6</v>
@@ -7601,37 +7601,37 @@
         <v>88.7</v>
       </c>
       <c r="M77">
-        <v>97.80183</v>
+        <v>99.1058544</v>
       </c>
       <c r="N77">
-        <v>-9.101829999999993</v>
+        <v>-10.4058544</v>
       </c>
       <c r="O77">
-        <v>-2.184439199999998</v>
+        <v>-2.497405055999999</v>
       </c>
       <c r="P77">
-        <v>-6.917390799999994</v>
+        <v>-7.908449343999997</v>
       </c>
       <c r="Q77">
-        <v>25.4826092</v>
+        <v>24.49155065599999</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1759144230150372</v>
+        <v>0.1813358573073304</v>
       </c>
       <c r="T77">
-        <v>2.675289484992221</v>
+        <v>2.786759880200231</v>
       </c>
       <c r="U77">
         <v>0.1468</v>
       </c>
       <c r="V77">
-        <v>0.2176646387905012</v>
+        <v>0.214800630385363</v>
       </c>
       <c r="W77">
-        <v>0.1148468310255544</v>
+        <v>0.1152672674594287</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.9069359949604215</v>
+        <v>0.8950026266056792</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1311237290229251</v>
+        <v>0.1321337290229251</v>
       </c>
       <c r="C78">
-        <v>-81.94152229133999</v>
+        <v>-93.73902976887734</v>
       </c>
       <c r="D78">
-        <v>299.5664777086599</v>
+        <v>296.6519702311226</v>
       </c>
       <c r="E78">
-        <v>273.0079999999999</v>
+        <v>281.891</v>
       </c>
       <c r="F78">
-        <v>675.1079999999999</v>
+        <v>683.991</v>
       </c>
       <c r="G78">
         <v>293.6</v>
@@ -7683,37 +7683,37 @@
         <v>88.7</v>
       </c>
       <c r="M78">
-        <v>99.1058544</v>
+        <v>100.4098788</v>
       </c>
       <c r="N78">
-        <v>-10.4058544</v>
+        <v>-11.7098788</v>
       </c>
       <c r="O78">
-        <v>-2.497405055999999</v>
+        <v>-2.810370911999999</v>
       </c>
       <c r="P78">
-        <v>-7.908449343999997</v>
+        <v>-8.899507887999999</v>
       </c>
       <c r="Q78">
-        <v>24.49155065599999</v>
+        <v>23.50049211199999</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1813358573073304</v>
+        <v>0.1872287206685186</v>
       </c>
       <c r="T78">
-        <v>2.786759880200231</v>
+        <v>2.907923353252415</v>
       </c>
       <c r="U78">
         <v>0.1468</v>
       </c>
       <c r="V78">
-        <v>0.214800630385363</v>
+        <v>0.2120110118089297</v>
       </c>
       <c r="W78">
-        <v>0.1152672674594287</v>
+        <v>0.1156767834664491</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.8950026266056792</v>
+        <v>0.8833792158705405</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1321337290229251</v>
+        <v>0.1331437290229251</v>
       </c>
       <c r="C79">
-        <v>-93.73902976887734</v>
+        <v>-105.4803726988721</v>
       </c>
       <c r="D79">
-        <v>296.6519702311226</v>
+        <v>293.793627301128</v>
       </c>
       <c r="E79">
-        <v>281.891</v>
+        <v>290.774</v>
       </c>
       <c r="F79">
-        <v>683.991</v>
+        <v>692.874</v>
       </c>
       <c r="G79">
         <v>293.6</v>
@@ -7765,37 +7765,37 @@
         <v>88.7</v>
       </c>
       <c r="M79">
-        <v>100.4098788</v>
+        <v>101.7139032</v>
       </c>
       <c r="N79">
-        <v>-11.7098788</v>
+        <v>-13.01390320000002</v>
       </c>
       <c r="O79">
-        <v>-2.810370911999999</v>
+        <v>-3.123336768000004</v>
       </c>
       <c r="P79">
-        <v>-8.899507887999999</v>
+        <v>-9.890566432000012</v>
       </c>
       <c r="Q79">
-        <v>23.50049211199999</v>
+        <v>22.50943356799998</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1872287206685186</v>
+        <v>0.193657298880724</v>
       </c>
       <c r="T79">
-        <v>2.907923353252415</v>
+        <v>3.040101687491161</v>
       </c>
       <c r="U79">
         <v>0.1468</v>
       </c>
       <c r="V79">
-        <v>0.2120110118089297</v>
+        <v>0.2092929219139434</v>
       </c>
       <c r="W79">
-        <v>0.1156767834664491</v>
+        <v>0.1160757990630331</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.8833792158705405</v>
+        <v>0.8720538413080975</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1331437290229251</v>
+        <v>0.1341537290229251</v>
       </c>
       <c r="C80">
-        <v>-105.4803726988721</v>
+        <v>-117.1671590814196</v>
       </c>
       <c r="D80">
-        <v>293.793627301128</v>
+        <v>290.9898409185803</v>
       </c>
       <c r="E80">
-        <v>290.774</v>
+        <v>299.6569999999999</v>
       </c>
       <c r="F80">
-        <v>692.874</v>
+        <v>701.7569999999999</v>
       </c>
       <c r="G80">
         <v>293.6</v>
@@ -7847,37 +7847,37 @@
         <v>88.7</v>
       </c>
       <c r="M80">
-        <v>101.7139032</v>
+        <v>103.0179276</v>
       </c>
       <c r="N80">
-        <v>-13.01390320000002</v>
+        <v>-14.3179276</v>
       </c>
       <c r="O80">
-        <v>-3.123336768000004</v>
+        <v>-3.436302624000001</v>
       </c>
       <c r="P80">
-        <v>-9.890566432000012</v>
+        <v>-10.881624976</v>
       </c>
       <c r="Q80">
-        <v>22.50943356799998</v>
+        <v>21.51837502399999</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.193657298880724</v>
+        <v>0.200698122636949</v>
       </c>
       <c r="T80">
-        <v>3.040101687491161</v>
+        <v>3.18486843451455</v>
       </c>
       <c r="U80">
         <v>0.1468</v>
       </c>
       <c r="V80">
-        <v>0.2092929219139434</v>
+        <v>0.2066436444213618</v>
       </c>
       <c r="W80">
-        <v>0.1160757990630331</v>
+        <v>0.1164647129989441</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.8720538413080975</v>
+        <v>0.8610151850890078</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1341537290229251</v>
+        <v>0.1351637290229251</v>
       </c>
       <c r="C81">
-        <v>-117.1671590814196</v>
+        <v>-128.8009361138091</v>
       </c>
       <c r="D81">
-        <v>290.9898409185803</v>
+        <v>288.2390638861909</v>
       </c>
       <c r="E81">
-        <v>299.6569999999999</v>
+        <v>308.54</v>
       </c>
       <c r="F81">
-        <v>701.7569999999999</v>
+        <v>710.64</v>
       </c>
       <c r="G81">
         <v>293.6</v>
@@ -7929,37 +7929,37 @@
         <v>88.7</v>
       </c>
       <c r="M81">
-        <v>103.0179276</v>
+        <v>104.321952</v>
       </c>
       <c r="N81">
-        <v>-14.3179276</v>
+        <v>-15.62195200000001</v>
       </c>
       <c r="O81">
-        <v>-3.436302624000001</v>
+        <v>-3.749268480000002</v>
       </c>
       <c r="P81">
-        <v>-10.881624976</v>
+        <v>-11.87268352000001</v>
       </c>
       <c r="Q81">
-        <v>21.51837502399999</v>
+        <v>20.52731647999999</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.200698122636949</v>
+        <v>0.2084430287687965</v>
       </c>
       <c r="T81">
-        <v>3.18486843451455</v>
+        <v>3.344111856240278</v>
       </c>
       <c r="U81">
         <v>0.1468</v>
       </c>
       <c r="V81">
-        <v>0.2066436444213618</v>
+        <v>0.2040605988660948</v>
       </c>
       <c r="W81">
-        <v>0.1164647129989441</v>
+        <v>0.1168439040864573</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.8610151850890078</v>
+        <v>0.8502524952753951</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1351637290229251</v>
+        <v>0.1361737290229251</v>
       </c>
       <c r="C82">
-        <v>-128.8009361138091</v>
+        <v>-140.3831930375076</v>
       </c>
       <c r="D82">
-        <v>288.2390638861909</v>
+        <v>285.5398069624925</v>
       </c>
       <c r="E82">
-        <v>308.54</v>
+        <v>317.423</v>
       </c>
       <c r="F82">
-        <v>710.64</v>
+        <v>719.523</v>
       </c>
       <c r="G82">
         <v>293.6</v>
@@ -8011,37 +8011,37 @@
         <v>88.7</v>
       </c>
       <c r="M82">
-        <v>104.321952</v>
+        <v>105.6259764</v>
       </c>
       <c r="N82">
-        <v>-15.62195200000001</v>
+        <v>-16.92597640000001</v>
       </c>
       <c r="O82">
-        <v>-3.749268480000002</v>
+        <v>-4.062234336000002</v>
       </c>
       <c r="P82">
-        <v>-11.87268352000001</v>
+        <v>-12.86374206400001</v>
       </c>
       <c r="Q82">
-        <v>20.52731647999999</v>
+        <v>19.53625793599998</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2084430287687965</v>
+        <v>0.2170031881776805</v>
       </c>
       <c r="T82">
-        <v>3.344111856240278</v>
+        <v>3.520117743410818</v>
       </c>
       <c r="U82">
         <v>0.1468</v>
       </c>
       <c r="V82">
-        <v>0.2040605988660948</v>
+        <v>0.201541332213427</v>
       </c>
       <c r="W82">
-        <v>0.1168439040864573</v>
+        <v>0.1172137324310689</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.8502524952753951</v>
+        <v>0.8397555508892791</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1361737290229251</v>
+        <v>0.1371837290229251</v>
       </c>
       <c r="C83">
-        <v>-140.3831930375076</v>
+        <v>-151.9153638266613</v>
       </c>
       <c r="D83">
-        <v>285.5398069624925</v>
+        <v>282.8906361733387</v>
       </c>
       <c r="E83">
-        <v>317.423</v>
+        <v>326.306</v>
       </c>
       <c r="F83">
-        <v>719.523</v>
+        <v>728.4060000000001</v>
       </c>
       <c r="G83">
         <v>293.6</v>
@@ -8093,37 +8093,37 @@
         <v>88.7</v>
       </c>
       <c r="M83">
-        <v>105.6259764</v>
+        <v>106.9300008</v>
       </c>
       <c r="N83">
-        <v>-16.92597640000001</v>
+        <v>-18.23000080000001</v>
       </c>
       <c r="O83">
-        <v>-4.062234336000002</v>
+        <v>-4.375200192000003</v>
       </c>
       <c r="P83">
-        <v>-12.86374206400001</v>
+        <v>-13.85480060800001</v>
       </c>
       <c r="Q83">
-        <v>19.53625793599998</v>
+        <v>18.54519939199998</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2170031881776805</v>
+        <v>0.2265144764097738</v>
       </c>
       <c r="T83">
-        <v>3.520117743410818</v>
+        <v>3.715679840266975</v>
       </c>
       <c r="U83">
         <v>0.1468</v>
       </c>
       <c r="V83">
-        <v>0.201541332213427</v>
+        <v>0.199083511088873</v>
       </c>
       <c r="W83">
-        <v>0.1172137324310689</v>
+        <v>0.1175745405721535</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.8397555508892791</v>
+        <v>0.8295146295369707</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1371837290229251</v>
+        <v>0.1381937290229251</v>
       </c>
       <c r="C84">
-        <v>-151.9153638266613</v>
+        <v>-163.3988297283147</v>
       </c>
       <c r="D84">
-        <v>282.8906361733387</v>
+        <v>280.2901702716853</v>
       </c>
       <c r="E84">
-        <v>326.306</v>
+        <v>335.189</v>
       </c>
       <c r="F84">
-        <v>728.4060000000001</v>
+        <v>737.289</v>
       </c>
       <c r="G84">
         <v>293.6</v>
@@ -8175,37 +8175,37 @@
         <v>88.7</v>
       </c>
       <c r="M84">
-        <v>106.9300008</v>
+        <v>108.2340252</v>
       </c>
       <c r="N84">
-        <v>-18.23000080000001</v>
+        <v>-19.5340252</v>
       </c>
       <c r="O84">
-        <v>-4.375200192000003</v>
+        <v>-4.688166048</v>
       </c>
       <c r="P84">
-        <v>-13.85480060800001</v>
+        <v>-14.845859152</v>
       </c>
       <c r="Q84">
-        <v>18.54519939199998</v>
+        <v>17.55414084799999</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2265144764097738</v>
+        <v>0.2371447397279959</v>
       </c>
       <c r="T84">
-        <v>3.715679840266975</v>
+        <v>3.934249242635621</v>
       </c>
       <c r="U84">
         <v>0.1468</v>
       </c>
       <c r="V84">
-        <v>0.199083511088873</v>
+        <v>0.1966849145697299</v>
       </c>
       <c r="W84">
-        <v>0.1175745405721535</v>
+        <v>0.1179266545411637</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.8295146295369707</v>
+        <v>0.8195204773738749</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1381937290229251</v>
+        <v>0.1392037290229251</v>
       </c>
       <c r="C85">
-        <v>-163.3988297283147</v>
+        <v>-174.8349216637988</v>
       </c>
       <c r="D85">
-        <v>280.2901702716853</v>
+        <v>277.7370783362012</v>
       </c>
       <c r="E85">
-        <v>335.189</v>
+        <v>344.072</v>
       </c>
       <c r="F85">
-        <v>737.289</v>
+        <v>746.172</v>
       </c>
       <c r="G85">
         <v>293.6</v>
@@ -8257,37 +8257,37 @@
         <v>88.7</v>
       </c>
       <c r="M85">
-        <v>108.2340252</v>
+        <v>109.5380496</v>
       </c>
       <c r="N85">
-        <v>-19.5340252</v>
+        <v>-20.83804960000001</v>
       </c>
       <c r="O85">
-        <v>-4.688166048</v>
+        <v>-5.001131904000001</v>
       </c>
       <c r="P85">
-        <v>-14.845859152</v>
+        <v>-15.836917696</v>
       </c>
       <c r="Q85">
-        <v>17.55414084799999</v>
+        <v>16.56308230399999</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2371447397279959</v>
+        <v>0.2491037859609956</v>
       </c>
       <c r="T85">
-        <v>3.934249242635621</v>
+        <v>4.180139820300348</v>
       </c>
       <c r="U85">
         <v>0.1468</v>
       </c>
       <c r="V85">
-        <v>0.1966849145697299</v>
+        <v>0.1943434274915189</v>
       </c>
       <c r="W85">
-        <v>0.1179266545411637</v>
+        <v>0.118270384844245</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.8195204773738749</v>
+        <v>0.809764281214662</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1392037290229251</v>
+        <v>0.1402137290229251</v>
       </c>
       <c r="C86">
-        <v>-174.8349216637987</v>
+        <v>-186.224922500063</v>
       </c>
       <c r="D86">
-        <v>277.7370783362012</v>
+        <v>275.2300774999369</v>
       </c>
       <c r="E86">
-        <v>344.0719999999999</v>
+        <v>352.9549999999999</v>
       </c>
       <c r="F86">
-        <v>746.1719999999999</v>
+        <v>755.0549999999999</v>
       </c>
       <c r="G86">
         <v>293.6</v>
@@ -8339,37 +8339,37 @@
         <v>88.7</v>
       </c>
       <c r="M86">
-        <v>109.5380496</v>
+        <v>110.842074</v>
       </c>
       <c r="N86">
-        <v>-20.83804959999999</v>
+        <v>-22.14207399999999</v>
       </c>
       <c r="O86">
-        <v>-5.001131903999998</v>
+        <v>-5.314097759999998</v>
       </c>
       <c r="P86">
-        <v>-15.83691769599999</v>
+        <v>-16.82797623999999</v>
       </c>
       <c r="Q86">
-        <v>16.563082304</v>
+        <v>15.57202376</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2491037859609955</v>
+        <v>0.2626573716917285</v>
       </c>
       <c r="T86">
-        <v>4.180139820300345</v>
+        <v>4.458815808320368</v>
       </c>
       <c r="U86">
         <v>0.1468</v>
       </c>
       <c r="V86">
-        <v>0.1943434274915189</v>
+        <v>0.1920570342269128</v>
       </c>
       <c r="W86">
-        <v>0.118270384844245</v>
+        <v>0.1186060273754892</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.8097642812146622</v>
+        <v>0.8002376426121367</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1402137290229251</v>
+        <v>0.1893703934394672</v>
       </c>
       <c r="C87">
-        <v>-186.224922500063</v>
+        <v>-279.1157927844991</v>
       </c>
       <c r="D87">
-        <v>275.2300774999369</v>
+        <v>191.2222072155009</v>
       </c>
       <c r="E87">
-        <v>352.9549999999999</v>
+        <v>361.838</v>
       </c>
       <c r="F87">
-        <v>755.0549999999999</v>
+        <v>763.938</v>
       </c>
       <c r="G87">
         <v>293.6</v>
@@ -8421,45 +8421,45 @@
         <v>88.7</v>
       </c>
       <c r="M87">
-        <v>110.842074</v>
+        <v>153.3987504</v>
       </c>
       <c r="N87">
-        <v>-22.14207399999999</v>
+        <v>-64.69875040000001</v>
       </c>
       <c r="O87">
-        <v>-5.314097759999998</v>
+        <v>-15.527700096</v>
       </c>
       <c r="P87">
-        <v>-16.82797623999999</v>
+        <v>-49.171050304</v>
       </c>
       <c r="Q87">
-        <v>15.57202376</v>
+        <v>-16.77105030400001</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2626573716917285</v>
+        <v>0.2903376440735809</v>
       </c>
       <c r="T87">
-        <v>4.458815808320368</v>
+        <v>5.027951342482727</v>
       </c>
       <c r="U87">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V87">
-        <v>0.1920570342269128</v>
+        <v>0.1387755763621918</v>
       </c>
       <c r="W87">
-        <v>0.1186060273754892</v>
+        <v>0.1729338642664719</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y87">
-        <v>0.8002376426121367</v>
+        <v>0.5782315681757991</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1893703934394672</v>
+        <v>0.1909203934394672</v>
       </c>
       <c r="C88">
-        <v>-279.1157927844991</v>
+        <v>-289.8216467054386</v>
       </c>
       <c r="D88">
-        <v>191.2222072155009</v>
+        <v>189.3993532945613</v>
       </c>
       <c r="E88">
-        <v>361.838</v>
+        <v>370.7209999999999</v>
       </c>
       <c r="F88">
-        <v>763.938</v>
+        <v>772.8209999999999</v>
       </c>
       <c r="G88">
         <v>293.6</v>
@@ -8503,37 +8503,37 @@
         <v>88.7</v>
       </c>
       <c r="M88">
-        <v>153.3987504</v>
+        <v>155.1824568</v>
       </c>
       <c r="N88">
-        <v>-64.69875040000001</v>
+        <v>-66.48245679999998</v>
       </c>
       <c r="O88">
-        <v>-15.527700096</v>
+        <v>-15.95578963199999</v>
       </c>
       <c r="P88">
-        <v>-49.171050304</v>
+        <v>-50.52666716799999</v>
       </c>
       <c r="Q88">
-        <v>-16.77105030400001</v>
+        <v>-18.126667168</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2903376440735809</v>
+        <v>0.309148232079241</v>
       </c>
       <c r="T88">
-        <v>5.027951342482727</v>
+        <v>5.414716830366014</v>
       </c>
       <c r="U88">
         <v>0.2008</v>
       </c>
       <c r="V88">
-        <v>0.1387755763621918</v>
+        <v>0.1371804547948103</v>
       </c>
       <c r="W88">
-        <v>0.1729338642664719</v>
+        <v>0.1732541646772021</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.5782315681757991</v>
+        <v>0.5715852283117095</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1909203934394672</v>
+        <v>0.1924703934394672</v>
       </c>
       <c r="C89">
-        <v>-289.8216467054386</v>
+        <v>-300.4930755403644</v>
       </c>
       <c r="D89">
-        <v>189.3993532945613</v>
+        <v>187.6109244596355</v>
       </c>
       <c r="E89">
-        <v>370.7209999999999</v>
+        <v>379.6039999999999</v>
       </c>
       <c r="F89">
-        <v>772.8209999999999</v>
+        <v>781.704</v>
       </c>
       <c r="G89">
         <v>293.6</v>
@@ -8585,37 +8585,37 @@
         <v>88.7</v>
       </c>
       <c r="M89">
-        <v>155.1824568</v>
+        <v>156.9661632</v>
       </c>
       <c r="N89">
-        <v>-66.48245679999998</v>
+        <v>-68.26616319999998</v>
       </c>
       <c r="O89">
-        <v>-15.95578963199999</v>
+        <v>-16.38387916799999</v>
       </c>
       <c r="P89">
-        <v>-50.52666716799999</v>
+        <v>-51.88228403199999</v>
       </c>
       <c r="Q89">
-        <v>-18.126667168</v>
+        <v>-19.482284032</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.309148232079241</v>
+        <v>0.3310939180858445</v>
       </c>
       <c r="T89">
-        <v>5.414716830366014</v>
+        <v>5.865943232896516</v>
       </c>
       <c r="U89">
         <v>0.2008</v>
       </c>
       <c r="V89">
-        <v>0.1371804547948103</v>
+        <v>0.1356215859903238</v>
       </c>
       <c r="W89">
-        <v>0.1732541646772021</v>
+        <v>0.173567185533143</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.5715852283117095</v>
+        <v>0.5650899416263493</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1924703934394672</v>
+        <v>0.1940203934394672</v>
       </c>
       <c r="C90">
-        <v>-300.4930755403644</v>
+        <v>-311.1310453575437</v>
       </c>
       <c r="D90">
-        <v>187.6109244596355</v>
+        <v>185.8559546424562</v>
       </c>
       <c r="E90">
-        <v>379.6039999999999</v>
+        <v>388.487</v>
       </c>
       <c r="F90">
-        <v>781.704</v>
+        <v>790.587</v>
       </c>
       <c r="G90">
         <v>293.6</v>
@@ -8667,37 +8667,37 @@
         <v>88.7</v>
       </c>
       <c r="M90">
-        <v>156.9661632</v>
+        <v>158.7498696</v>
       </c>
       <c r="N90">
-        <v>-68.26616319999998</v>
+        <v>-70.04986960000001</v>
       </c>
       <c r="O90">
-        <v>-16.38387916799999</v>
+        <v>-16.811968704</v>
       </c>
       <c r="P90">
-        <v>-51.88228403199999</v>
+        <v>-53.23790089600001</v>
       </c>
       <c r="Q90">
-        <v>-19.482284032</v>
+        <v>-20.83790089600001</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3310939180858445</v>
+        <v>0.3570297288209212</v>
       </c>
       <c r="T90">
-        <v>5.865943232896516</v>
+        <v>6.399210799523471</v>
       </c>
       <c r="U90">
         <v>0.2008</v>
       </c>
       <c r="V90">
-        <v>0.1356215859903238</v>
+        <v>0.1340977479454887</v>
       </c>
       <c r="W90">
-        <v>0.173567185533143</v>
+        <v>0.1738731722125459</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.5650899416263493</v>
+        <v>0.5587406164395363</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1940203934394672</v>
+        <v>0.1955703934394671</v>
       </c>
       <c r="C91">
-        <v>-311.1310453575437</v>
+        <v>-321.7364864126566</v>
       </c>
       <c r="D91">
-        <v>185.8559546424562</v>
+        <v>184.1335135873434</v>
       </c>
       <c r="E91">
-        <v>388.487</v>
+        <v>397.37</v>
       </c>
       <c r="F91">
-        <v>790.587</v>
+        <v>799.47</v>
       </c>
       <c r="G91">
         <v>293.6</v>
@@ -8749,37 +8749,37 @@
         <v>88.7</v>
       </c>
       <c r="M91">
-        <v>158.7498696</v>
+        <v>160.533576</v>
       </c>
       <c r="N91">
-        <v>-70.04986960000001</v>
+        <v>-71.83357600000001</v>
       </c>
       <c r="O91">
-        <v>-16.811968704</v>
+        <v>-17.24005824</v>
       </c>
       <c r="P91">
-        <v>-53.23790089600001</v>
+        <v>-54.59351776000001</v>
       </c>
       <c r="Q91">
-        <v>-20.83790089600001</v>
+        <v>-22.19351776000002</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3570297288209212</v>
+        <v>0.3881527017030134</v>
       </c>
       <c r="T91">
-        <v>6.399210799523471</v>
+        <v>7.03913187947582</v>
       </c>
       <c r="U91">
         <v>0.2008</v>
       </c>
       <c r="V91">
-        <v>0.1340977479454887</v>
+        <v>0.1326077729683166</v>
       </c>
       <c r="W91">
-        <v>0.1738731722125459</v>
+        <v>0.174172359187962</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.5587406164395363</v>
+        <v>0.5525323873679859</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1955703934394671</v>
+        <v>0.1971203934394672</v>
       </c>
       <c r="C92">
-        <v>-321.7364864126566</v>
+        <v>-332.3102947930437</v>
       </c>
       <c r="D92">
-        <v>184.1335135873434</v>
+        <v>182.4427052069562</v>
       </c>
       <c r="E92">
-        <v>397.37</v>
+        <v>406.2529999999999</v>
       </c>
       <c r="F92">
-        <v>799.47</v>
+        <v>808.353</v>
       </c>
       <c r="G92">
         <v>293.6</v>
@@ -8831,37 +8831,37 @@
         <v>88.7</v>
       </c>
       <c r="M92">
-        <v>160.533576</v>
+        <v>162.3172824</v>
       </c>
       <c r="N92">
-        <v>-71.83357600000001</v>
+        <v>-73.61728239999998</v>
       </c>
       <c r="O92">
-        <v>-17.24005824</v>
+        <v>-17.66814777599999</v>
       </c>
       <c r="P92">
-        <v>-54.59351776000001</v>
+        <v>-55.94913462399998</v>
       </c>
       <c r="Q92">
-        <v>-22.19351776000002</v>
+        <v>-23.54913462399999</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.3881527017030134</v>
+        <v>0.426191890781126</v>
       </c>
       <c r="T92">
-        <v>7.03913187947582</v>
+        <v>7.821257643862022</v>
       </c>
       <c r="U92">
         <v>0.2008</v>
       </c>
       <c r="V92">
-        <v>0.1326077729683166</v>
+        <v>0.1311505446939395</v>
       </c>
       <c r="W92">
-        <v>0.174172359187962</v>
+        <v>0.174464970625457</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.5525323873679859</v>
+        <v>0.5464606028914147</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1971203934394672</v>
+        <v>0.1986703934394672</v>
       </c>
       <c r="C93">
-        <v>-332.3102947930437</v>
+        <v>-342.8533339721884</v>
       </c>
       <c r="D93">
-        <v>182.4427052069562</v>
+        <v>180.7826660278116</v>
       </c>
       <c r="E93">
-        <v>406.2529999999999</v>
+        <v>415.136</v>
       </c>
       <c r="F93">
-        <v>808.353</v>
+        <v>817.236</v>
       </c>
       <c r="G93">
         <v>293.6</v>
@@ -8913,37 +8913,37 @@
         <v>88.7</v>
       </c>
       <c r="M93">
-        <v>162.3172824</v>
+        <v>164.1009888</v>
       </c>
       <c r="N93">
-        <v>-73.61728239999998</v>
+        <v>-75.40098880000001</v>
       </c>
       <c r="O93">
-        <v>-17.66814777599999</v>
+        <v>-18.096237312</v>
       </c>
       <c r="P93">
-        <v>-55.94913462399998</v>
+        <v>-57.30475148800001</v>
       </c>
       <c r="Q93">
-        <v>-23.54913462399999</v>
+        <v>-24.90475148800002</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.426191890781126</v>
+        <v>0.4737408771287668</v>
       </c>
       <c r="T93">
-        <v>7.821257643862022</v>
+        <v>8.798914849344778</v>
       </c>
       <c r="U93">
         <v>0.2008</v>
       </c>
       <c r="V93">
-        <v>0.1311505446939395</v>
+        <v>0.1297249952950923</v>
       </c>
       <c r="W93">
-        <v>0.174464970625457</v>
+        <v>0.1747512209447455</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.5464606028914147</v>
+        <v>0.5405208137295514</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1986703934394672</v>
+        <v>0.2002203934394672</v>
       </c>
       <c r="C94">
-        <v>-342.8533339721884</v>
+        <v>-353.3664362800986</v>
       </c>
       <c r="D94">
-        <v>180.7826660278116</v>
+        <v>179.1525637199015</v>
       </c>
       <c r="E94">
-        <v>415.136</v>
+        <v>424.019</v>
       </c>
       <c r="F94">
-        <v>817.236</v>
+        <v>826.119</v>
       </c>
       <c r="G94">
         <v>293.6</v>
@@ -8995,37 +8995,37 @@
         <v>88.7</v>
       </c>
       <c r="M94">
-        <v>164.1009888</v>
+        <v>165.8846952</v>
       </c>
       <c r="N94">
-        <v>-75.40098880000001</v>
+        <v>-77.18469520000001</v>
       </c>
       <c r="O94">
-        <v>-18.096237312</v>
+        <v>-18.524326848</v>
       </c>
       <c r="P94">
-        <v>-57.30475148800001</v>
+        <v>-58.66036835200001</v>
       </c>
       <c r="Q94">
-        <v>-24.90475148800002</v>
+        <v>-26.26036835200001</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.4737408771287668</v>
+        <v>0.5348752881471622</v>
       </c>
       <c r="T94">
-        <v>8.798914849344778</v>
+        <v>10.05590268496546</v>
       </c>
       <c r="U94">
         <v>0.2008</v>
       </c>
       <c r="V94">
-        <v>0.1297249952950923</v>
+        <v>0.1283301028725645</v>
       </c>
       <c r="W94">
-        <v>0.1747512209447455</v>
+        <v>0.1750313153431891</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.5405208137295514</v>
+        <v>0.5347087619690185</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2002203934394672</v>
+        <v>0.2017703934394671</v>
       </c>
       <c r="C95">
-        <v>-353.3664362800986</v>
+        <v>-363.8504042948504</v>
       </c>
       <c r="D95">
-        <v>179.1525637199015</v>
+        <v>177.5515957051495</v>
       </c>
       <c r="E95">
-        <v>424.019</v>
+        <v>432.9019999999999</v>
       </c>
       <c r="F95">
-        <v>826.119</v>
+        <v>835.002</v>
       </c>
       <c r="G95">
         <v>293.6</v>
@@ -9077,37 +9077,37 @@
         <v>88.7</v>
       </c>
       <c r="M95">
-        <v>165.8846952</v>
+        <v>167.6684016</v>
       </c>
       <c r="N95">
-        <v>-77.18469520000001</v>
+        <v>-78.96840160000001</v>
       </c>
       <c r="O95">
-        <v>-18.524326848</v>
+        <v>-18.952416384</v>
       </c>
       <c r="P95">
-        <v>-58.66036835200001</v>
+        <v>-60.015985216</v>
       </c>
       <c r="Q95">
-        <v>-26.26036835200001</v>
+        <v>-27.61598521600001</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.5348752881471622</v>
+        <v>0.6163878361716892</v>
       </c>
       <c r="T95">
-        <v>10.05590268496546</v>
+        <v>11.73188646579304</v>
       </c>
       <c r="U95">
         <v>0.2008</v>
       </c>
       <c r="V95">
-        <v>0.1283301028725645</v>
+        <v>0.126964889012218</v>
       </c>
       <c r="W95">
-        <v>0.1750313153431891</v>
+        <v>0.1753054502863466</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.5347087619690185</v>
+        <v>0.5290203708842418</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2017703934394671</v>
+        <v>0.2033203934394672</v>
       </c>
       <c r="C96">
-        <v>-363.8504042948504</v>
+        <v>-374.3060121601806</v>
       </c>
       <c r="D96">
-        <v>177.5515957051495</v>
+        <v>175.9789878398194</v>
       </c>
       <c r="E96">
-        <v>432.9019999999999</v>
+        <v>441.785</v>
       </c>
       <c r="F96">
-        <v>835.002</v>
+        <v>843.885</v>
       </c>
       <c r="G96">
         <v>293.6</v>
@@ -9159,37 +9159,37 @@
         <v>88.7</v>
       </c>
       <c r="M96">
-        <v>167.6684016</v>
+        <v>169.452108</v>
       </c>
       <c r="N96">
-        <v>-78.96840160000001</v>
+        <v>-80.75210800000001</v>
       </c>
       <c r="O96">
-        <v>-18.952416384</v>
+        <v>-19.38050592</v>
       </c>
       <c r="P96">
-        <v>-60.015985216</v>
+        <v>-61.37160208</v>
       </c>
       <c r="Q96">
-        <v>-27.61598521600001</v>
+        <v>-28.97160208000001</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.6163878361716892</v>
+        <v>0.7305054034060274</v>
       </c>
       <c r="T96">
-        <v>11.73188646579304</v>
+        <v>14.07826375895166</v>
       </c>
       <c r="U96">
         <v>0.2008</v>
       </c>
       <c r="V96">
-        <v>0.126964889012218</v>
+        <v>0.1256284164962999</v>
       </c>
       <c r="W96">
-        <v>0.1753054502863466</v>
+        <v>0.175573813967543</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.5290203708842418</v>
+        <v>0.5234517354012498</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2033203934394672</v>
+        <v>0.2048703934394672</v>
       </c>
       <c r="C97">
-        <v>-374.3060121601806</v>
+        <v>-384.7340068336717</v>
       </c>
       <c r="D97">
-        <v>175.9789878398194</v>
+        <v>174.4339931663283</v>
       </c>
       <c r="E97">
-        <v>441.785</v>
+        <v>450.668</v>
       </c>
       <c r="F97">
-        <v>843.885</v>
+        <v>852.768</v>
       </c>
       <c r="G97">
         <v>293.6</v>
@@ -9241,37 +9241,37 @@
         <v>88.7</v>
       </c>
       <c r="M97">
-        <v>169.452108</v>
+        <v>171.2358144</v>
       </c>
       <c r="N97">
-        <v>-80.75210800000001</v>
+        <v>-82.53581440000001</v>
       </c>
       <c r="O97">
-        <v>-19.38050592</v>
+        <v>-19.808595456</v>
       </c>
       <c r="P97">
-        <v>-61.37160208</v>
+        <v>-62.727218944</v>
       </c>
       <c r="Q97">
-        <v>-28.97160208000001</v>
+        <v>-30.32721894400001</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.7305054034060274</v>
+        <v>0.9016817542575348</v>
       </c>
       <c r="T97">
-        <v>14.07826375895166</v>
+        <v>17.59782969868958</v>
       </c>
       <c r="U97">
         <v>0.2008</v>
       </c>
       <c r="V97">
-        <v>0.1256284164962999</v>
+        <v>0.1243197871577968</v>
       </c>
       <c r="W97">
-        <v>0.175573813967543</v>
+        <v>0.1758365867387144</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.5234517354012498</v>
+        <v>0.5179991131574868</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2048703934394672</v>
+        <v>0.2064203934394672</v>
       </c>
       <c r="C98">
-        <v>-384.7340068336716</v>
+        <v>-395.1351092697611</v>
       </c>
       <c r="D98">
-        <v>174.4339931663283</v>
+        <v>172.9158907302388</v>
       </c>
       <c r="E98">
-        <v>450.6679999999999</v>
+        <v>459.5509999999999</v>
       </c>
       <c r="F98">
-        <v>852.7679999999999</v>
+        <v>861.651</v>
       </c>
       <c r="G98">
         <v>293.6</v>
@@ -9323,37 +9323,37 @@
         <v>88.7</v>
       </c>
       <c r="M98">
-        <v>171.2358144</v>
+        <v>173.0195208</v>
       </c>
       <c r="N98">
-        <v>-82.53581439999998</v>
+        <v>-84.31952080000001</v>
       </c>
       <c r="O98">
-        <v>-19.808595456</v>
+        <v>-20.236684992</v>
       </c>
       <c r="P98">
-        <v>-62.72721894399999</v>
+        <v>-64.082835808</v>
       </c>
       <c r="Q98">
-        <v>-30.32721894399999</v>
+        <v>-31.68283580800001</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.9016817542575325</v>
+        <v>1.186975672343377</v>
       </c>
       <c r="T98">
-        <v>17.59782969868953</v>
+        <v>23.46377293158604</v>
       </c>
       <c r="U98">
         <v>0.2008</v>
       </c>
       <c r="V98">
-        <v>0.1243197871577968</v>
+        <v>0.1230381398675103</v>
       </c>
       <c r="W98">
-        <v>0.1758365867387144</v>
+        <v>0.1760939415146039</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.5179991131574868</v>
+        <v>0.512658916114626</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2064203934394672</v>
+        <v>0.2079703934394672</v>
       </c>
       <c r="C99">
-        <v>-395.1351092697611</v>
+        <v>-405.5100155415075</v>
       </c>
       <c r="D99">
-        <v>172.9158907302388</v>
+        <v>171.4239844584924</v>
       </c>
       <c r="E99">
-        <v>459.5509999999999</v>
+        <v>468.434</v>
       </c>
       <c r="F99">
-        <v>861.651</v>
+        <v>870.534</v>
       </c>
       <c r="G99">
         <v>293.6</v>
@@ -9405,37 +9405,37 @@
         <v>88.7</v>
       </c>
       <c r="M99">
-        <v>173.0195208</v>
+        <v>174.8032272</v>
       </c>
       <c r="N99">
-        <v>-84.31952080000001</v>
+        <v>-86.10322720000001</v>
       </c>
       <c r="O99">
-        <v>-20.236684992</v>
+        <v>-20.664774528</v>
       </c>
       <c r="P99">
-        <v>-64.082835808</v>
+        <v>-65.43845267200001</v>
       </c>
       <c r="Q99">
-        <v>-31.68283580800001</v>
+        <v>-33.03845267200002</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.186975672343377</v>
+        <v>1.757563508515065</v>
       </c>
       <c r="T99">
-        <v>23.46377293158604</v>
+        <v>35.19565939737906</v>
       </c>
       <c r="U99">
         <v>0.2008</v>
       </c>
       <c r="V99">
-        <v>0.1230381398675103</v>
+        <v>0.1217826486443724</v>
       </c>
       <c r="W99">
-        <v>0.1760939415146039</v>
+        <v>0.17634604415221</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.512658916114626</v>
+        <v>0.507427702684885</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2079703934394672</v>
+        <v>0.2095203934394671</v>
       </c>
       <c r="C100">
-        <v>-405.5100155415075</v>
+        <v>-415.8593979047824</v>
       </c>
       <c r="D100">
-        <v>171.4239844584924</v>
+        <v>169.9576020952174</v>
       </c>
       <c r="E100">
-        <v>468.434</v>
+        <v>477.3169999999999</v>
       </c>
       <c r="F100">
-        <v>870.534</v>
+        <v>879.4169999999999</v>
       </c>
       <c r="G100">
         <v>293.6</v>
@@ -9487,37 +9487,37 @@
         <v>88.7</v>
       </c>
       <c r="M100">
-        <v>174.8032272</v>
+        <v>176.5869336</v>
       </c>
       <c r="N100">
-        <v>-86.10322720000001</v>
+        <v>-87.88693359999998</v>
       </c>
       <c r="O100">
-        <v>-20.664774528</v>
+        <v>-21.09286406399999</v>
       </c>
       <c r="P100">
-        <v>-65.43845267200001</v>
+        <v>-66.79406953599998</v>
       </c>
       <c r="Q100">
-        <v>-33.03845267200002</v>
+        <v>-34.39406953599999</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.757563508515065</v>
+        <v>3.46932701703013</v>
       </c>
       <c r="T100">
-        <v>35.19565939737906</v>
+        <v>70.39131879475812</v>
       </c>
       <c r="U100">
         <v>0.2008</v>
       </c>
       <c r="V100">
-        <v>0.1217826486443724</v>
+        <v>0.1205525208802879</v>
       </c>
       <c r="W100">
-        <v>0.17634604415221</v>
+        <v>0.1765930538072382</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.507427702684885</v>
+        <v>0.5023021703345327</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2095203934394671</v>
-      </c>
-      <c r="C101">
-        <v>-415.8593979047824</v>
-      </c>
-      <c r="D101">
-        <v>169.9576020952174</v>
-      </c>
-      <c r="E101">
-        <v>477.3169999999999</v>
-      </c>
-      <c r="F101">
-        <v>879.4169999999999</v>
-      </c>
-      <c r="G101">
-        <v>293.6</v>
-      </c>
-      <c r="H101">
-        <v>486.2</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>121.1</v>
-      </c>
-      <c r="K101">
-        <v>32.39999999999999</v>
-      </c>
-      <c r="L101">
-        <v>88.7</v>
-      </c>
-      <c r="M101">
-        <v>176.5869336</v>
-      </c>
-      <c r="N101">
-        <v>-87.88693359999998</v>
-      </c>
-      <c r="O101">
-        <v>-21.09286406399999</v>
-      </c>
-      <c r="P101">
-        <v>-66.79406953599998</v>
-      </c>
-      <c r="Q101">
-        <v>-34.39406953599999</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.46932701703013</v>
-      </c>
-      <c r="T101">
-        <v>70.39131879475812</v>
-      </c>
-      <c r="U101">
-        <v>0.2008</v>
-      </c>
-      <c r="V101">
-        <v>0.1205525208802879</v>
-      </c>
-      <c r="W101">
-        <v>0.1765930538072382</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>C2/C</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.5023021703345327</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
